--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1159,10 +1159,10 @@
       <c r="G4" s="11" t="n"/>
       <c r="H4" s="11" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="50" customHeight="1">
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Maçã com casca</t>
+          <t>Maçã fuji (com casca)</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr"/>
@@ -1182,7 +1182,11 @@
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr"/>
-      <c r="H5" s="12" t="inlineStr"/>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Vale para maçã em geral, com casca (mais fibra) — Fuji é só um pouco mais doce que outras variedades, sem diferença relevante para o quadro do paciente.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="B6" s="12" t="inlineStr">
@@ -4132,7 +4136,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maçã com casca</t>
+          <t>Maçã fuji (com casca)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4155,7 +4159,11 @@
           <t>1x/dia</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vale para maçã em geral, com casca (mais fibra) — Fuji é só um pouco mais doce que outras variedades, sem diferença relevante para o quadro do paciente.</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>X</t>
@@ -4170,7 +4178,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Maçã com casca</t>
+          <t>Maçã fuji (com casca)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -4180,7 +4188,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Maçã com casca</t>
+          <t>Maçã fuji (com casca)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -4195,7 +4203,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Maçã com casca</t>
+          <t>Maçã fuji (com casca)</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5291,7 +5299,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Maçã com casca</t>
+          <t>Maçã fuji (com casca)</t>
         </is>
       </c>
     </row>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1488,53 +1488,57 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="148" customHeight="1">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Granola zero açúcar</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Castanha do Bem</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>20 g (1 colher de sopa)</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Rótulo real (porção 20 g): 83 kcal, 2,8 g de gordura (0,9 g saturada), 12 g de carboidrato, 1,1 g de açúcar (zero adicionado, adoçada com esteviol), 3 g de proteína, 2 g de fibra e 19 mg de sódio. Feita com aveia, coco, amêndoa, castanha de caju, castanha do pará e uva-passa — sem açúcar refinado, mas é calórica (415 kcal/100 g) e tem gordura saturada das castanhas/coco: manter na porção indicada, sem repetir a colher. Contém glúten; rótulo declara conter lactose (apesar de não haver laticínio nos ingredientes — provavelmente contaminação cruzada declarada); pode conter amendoim, avelã, centeio, leite, macadâmia, nozes, ovos, pecã, soja e trigo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Proteínas</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Peixe</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr"/>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>150 g</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr"/>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr"/>
@@ -1545,7 +1549,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1554,12 +1558,16 @@
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="12" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr"/>
@@ -1570,61 +1578,61 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+      <c r="H20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -1635,60 +1643,60 @@
       <c r="G22" s="13" t="inlineStr"/>
       <c r="H22" s="12" t="inlineStr"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Feijão / leguminosas</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr"/>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>1 concha</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Laticínios</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Leite desnatado</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25" ht="50" customHeight="1">
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr"/>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1697,26 +1705,18 @@
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+      <c r="H25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="50" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Polenghi</t>
-        </is>
-      </c>
+          <t>Queijo branco frescal</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr"/>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1732,82 +1732,82 @@
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="50" customHeight="1">
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Mussarela</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr"/>
+          <t>Queijo frescal light</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Polenghi</t>
+        </is>
+      </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="50" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr"/>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="50" customHeight="1">
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Vigor</t>
-        </is>
-      </c>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr"/>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1823,194 +1823,198 @@
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="50" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Requeijão</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr"/>
+          <t>Iogurte grego zero</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Vigor</t>
+        </is>
+      </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="12" t="inlineStr">
         <is>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr"/>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (≈15 g)</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr"/>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
           <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr"/>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr"/>
-      <c r="H32" s="12" t="inlineStr"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr"/>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr"/>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr"/>
-      <c r="H34" s="12" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr"/>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr"/>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="64" customHeight="1">
+      <c r="H35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr"/>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr"/>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr"/>
@@ -2032,57 +2036,57 @@
       <c r="G37" s="13" t="inlineStr"/>
       <c r="H37" s="12" t="inlineStr">
         <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr"/>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr"/>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr"/>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr"/>
@@ -2102,233 +2106,262 @@
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr"/>
-      <c r="H40" s="12" t="inlineStr"/>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr"/>
       <c r="D41" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr"/>
+      <c r="H41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr"/>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr"/>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr"/>
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="11" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="inlineStr"/>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr"/>
-      <c r="H43" s="12" t="inlineStr"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr"/>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H44" s="12" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr"/>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr"/>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr"/>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr"/>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr"/>
       <c r="D47" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr"/>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr"/>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr"/>
+      <c r="H48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr"/>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr"/>
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr"/>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2336,20 +2369,20 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G18 G19 G20 G21 G22 G24 G25 G26 G27 G28 G29 G30 G32 G33 G34 G35 G36 G37 G39 G40 G41 G43 G44 G45 G46 G47 G49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G25 G26 G27 G28 G29 G30 G31 G33 G34 G35 G36 G37 G38 G40 G41 G42 G44 G45 G46 G47 G48 G50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4038,7 +4071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4604,7 +4637,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Granola zero açúcar</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4674,7 +4707,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Granola zero açúcar</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4684,7 +4717,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4758,7 +4791,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4768,7 +4801,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4838,7 +4871,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4848,7 +4881,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4908,7 +4941,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4918,7 +4951,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4982,7 +5015,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4992,7 +5025,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5014,12 +5047,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Granola zero açúcar</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Proteínas</t>
+          <t>Grãos e Cereais</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5029,34 +5062,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>20 g (1 colher de sopa)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Rótulo real (porção 20 g): 83 kcal, 2,8 g de gordura (0,9 g saturada), 12 g de carboidrato, 1,1 g de açúcar (zero adicionado, adoçada com esteviol), 3 g de proteína, 2 g de fibra e 19 mg de sódio. Feita com aveia, coco, amêndoa, castanha de caju, castanha do pará e uva-passa — sem açúcar refinado, mas é calórica (415 kcal/100 g) e tem gordura saturada das castanhas/coco: manter na porção indicada, sem repetir a colher. Contém glúten; rótulo declara conter lactose (apesar de não haver laticínio nos ingredientes — provavelmente contaminação cruzada declarada); pode conter amendoim, avelã, centeio, leite, macadâmia, nozes, ovos, pecã, soja e trigo.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5066,7 +5099,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5088,7 +5121,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5108,10 +5141,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
@@ -5126,7 +5163,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5136,7 +5173,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -5158,7 +5195,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5168,7 +5205,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5178,14 +5215,10 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
@@ -5200,7 +5233,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5210,7 +5243,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -5232,7 +5265,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5242,25 +5275,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>X</t>
@@ -5274,7 +5307,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5284,7 +5317,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5306,7 +5339,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5321,16 +5354,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>X</t>
@@ -5344,7 +5381,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5354,7 +5391,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5376,12 +5413,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Laticínios</t>
+          <t>Proteínas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5391,7 +5428,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 concha</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5400,26 +5437,26 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5436,7 +5473,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5451,19 +5488,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>X</t>
@@ -5478,12 +5511,12 @@
       <c r="J19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5500,7 +5533,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5515,7 +5548,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5525,7 +5558,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5542,12 +5575,12 @@
       <c r="J20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5564,7 +5597,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5574,22 +5607,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5606,12 +5639,12 @@
       <c r="J21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>Suco natural sem açúcar</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5628,7 +5661,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5638,22 +5671,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5670,12 +5703,12 @@
       <c r="J22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -5692,7 +5725,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5707,7 +5740,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5717,7 +5750,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5734,12 +5767,12 @@
       <c r="J23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5756,7 +5789,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5766,22 +5799,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5798,12 +5831,12 @@
       <c r="J24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -5820,58 +5853,54 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -5888,7 +5917,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5898,25 +5927,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>X</t>
@@ -5930,6 +5959,16 @@
       <c r="J26" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -5946,7 +5985,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5956,32 +5995,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>Vegetais e Verduras|Jantar</t>
@@ -5996,7 +6043,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6006,24 +6053,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>X</t>
@@ -6040,7 +6083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6050,22 +6093,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -6084,7 +6127,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6109,31 +6152,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6153,24 +6196,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>X</t>
@@ -6180,7 +6215,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6203,20 +6238,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6226,24 +6277,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
@@ -6256,47 +6303,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6306,37 +6353,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6346,41 +6393,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6390,22 +6433,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Somar sal de cozinha + industrializados</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -6424,7 +6467,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6434,20 +6477,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
@@ -6464,50 +6511,90 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -230,6 +230,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1264,7 +1267,11 @@
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
           <t>Mais açúcar que outras frutas</t>
@@ -1317,7 +1324,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2028,7 +2035,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2057,7 +2064,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2100,7 +2107,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2129,7 +2136,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2222,7 +2229,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2280,7 +2287,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2361,7 +2368,7 @@
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2417,41 +2424,41 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Escolha o alimento no menu suspenso da coluna 'Alimento' — a lista já vem filtrada por refeição (por isso não aparece arroz/feijão no café da manhã, por exemplo) e com os alimentos Liberados primeiro. Categoria, Porção sugerida e Classificação preenchem sozinhas. 'Sugestão' mostra um alimento que costuma combinar bem com o item escolhido logo acima (é uma dica, não é obrigatório escolher). Se 'Conflito' mostrar '⚠ Conflito', evite reunir esses itens na mesma refeição.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Legenda:</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>⚠ Conflito</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>CAFÉ DA MANHÃ</t>
         </is>
@@ -2465,181 +2472,181 @@
       <c r="H5" s="11" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="26" t="n"/>
-      <c r="C7" s="27">
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E7" s="25" t="n"/>
-      <c r="F7" s="29">
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G7" s="30" t="inlineStr"/>
-      <c r="H7" s="31">
+      <c r="G7" s="31" t="inlineStr"/>
+      <c r="H7" s="32">
         <f>IF($B7="","",IF($F7="Evitar","⚠ Conflito",IF(AND($F7="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B7))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="n"/>
-      <c r="C8" s="27">
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="29">
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <f>IF($B7="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C7,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>IF($B8="","",IF($F8="Evitar","⚠ Conflito",IF(AND($F8="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B8))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="26" t="n"/>
-      <c r="C9" s="27">
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="29">
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>IF($B8="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C8,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>IF($B9="","",IF($F9="Evitar","⚠ Conflito",IF(AND($F9="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B9))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="27">
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="29">
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>IF($B9="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C9,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>IF($B10="","",IF($F10="Evitar","⚠ Conflito",IF(AND($F10="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B10))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="27">
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="29">
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>IF($B10="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C10,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>IF($B11="","",IF($F11="Evitar","⚠ Conflito",IF(AND($F11="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B11))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>ALMOÇO</t>
         </is>
@@ -2653,181 +2660,181 @@
       <c r="H13" s="11" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="27">
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="29">
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="30" t="inlineStr"/>
-      <c r="H15" s="31">
+      <c r="G15" s="31" t="inlineStr"/>
+      <c r="H15" s="32">
         <f>IF($B15="","",IF($F15="Evitar","⚠ Conflito",IF(AND($F15="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B15))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="27">
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="29">
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <f>IF($B15="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C15,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>IF($B16="","",IF($F16="Evitar","⚠ Conflito",IF(AND($F16="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B16))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="27">
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="29">
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>IF($B16="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C16,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>IF($B17="","",IF($F17="Evitar","⚠ Conflito",IF(AND($F17="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B17))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="27">
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="29">
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="31">
         <f>IF($B17="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C17,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="32">
         <f>IF($B18="","",IF($F18="Evitar","⚠ Conflito",IF(AND($F18="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B18))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="27">
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="29">
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="31">
         <f>IF($B18="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C18,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="32">
         <f>IF($B19="","",IF($F19="Evitar","⚠ Conflito",IF(AND($F19="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B19))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>LANCHE</t>
         </is>
@@ -2841,181 +2848,181 @@
       <c r="H21" s="11" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G22" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H22" s="24" t="inlineStr">
+      <c r="H22" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="25" t="n">
+      <c r="A23" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="27">
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="29">
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="30" t="inlineStr"/>
-      <c r="H23" s="31">
+      <c r="G23" s="31" t="inlineStr"/>
+      <c r="H23" s="32">
         <f>IF($B23="","",IF($F23="Evitar","⚠ Conflito",IF(AND($F23="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B23))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="25" t="n">
+      <c r="A24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="27">
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="29">
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <f>IF($B23="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C23,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <f>IF($B24="","",IF($F24="Evitar","⚠ Conflito",IF(AND($F24="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B24))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="25" t="n">
+      <c r="A25" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="26" t="n"/>
-      <c r="C25" s="27">
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="29">
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <f>IF($B24="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C24,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <f>IF($B25="","",IF($F25="Evitar","⚠ Conflito",IF(AND($F25="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B25))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="25" t="n">
+      <c r="A26" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="27">
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="29">
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="31">
         <f>IF($B25="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C25,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="32">
         <f>IF($B26="","",IF($F26="Evitar","⚠ Conflito",IF(AND($F26="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B26))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="25" t="n">
+      <c r="A27" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="27">
+      <c r="B27" s="27" t="n"/>
+      <c r="C27" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="29">
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <f>IF($B26="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C26,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <f>IF($B27="","",IF($F27="Evitar","⚠ Conflito",IF(AND($F27="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B27))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>JANTAR</t>
         </is>
@@ -3029,175 +3036,175 @@
       <c r="H29" s="11" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F30" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G30" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H30" s="24" t="inlineStr">
+      <c r="H30" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="25" t="n">
+      <c r="A31" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="27">
+      <c r="B31" s="27" t="n"/>
+      <c r="C31" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="29">
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="30" t="inlineStr"/>
-      <c r="H31" s="31">
+      <c r="G31" s="31" t="inlineStr"/>
+      <c r="H31" s="32">
         <f>IF($B31="","",IF($F31="Evitar","⚠ Conflito",IF(AND($F31="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B31))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="25" t="n">
+      <c r="A32" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="27">
+      <c r="B32" s="27" t="n"/>
+      <c r="C32" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="29">
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="31">
         <f>IF($B31="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C31,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H32" s="31">
+      <c r="H32" s="32">
         <f>IF($B32="","",IF($F32="Evitar","⚠ Conflito",IF(AND($F32="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B32))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="25" t="n">
+      <c r="A33" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="27">
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="25" t="n"/>
-      <c r="F33" s="29">
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="31">
         <f>IF($B32="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C32,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="32">
         <f>IF($B33="","",IF($F33="Evitar","⚠ Conflito",IF(AND($F33="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B33))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="25" t="n">
+      <c r="A34" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="27">
+      <c r="B34" s="27" t="n"/>
+      <c r="C34" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="29">
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="31">
         <f>IF($B33="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C33,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="32">
         <f>IF($B34="","",IF($F34="Evitar","⚠ Conflito",IF(AND($F34="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B34))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="25" t="n">
+      <c r="A35" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B35" s="26" t="n"/>
-      <c r="C35" s="27">
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="25" t="n"/>
-      <c r="F35" s="29">
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="31">
         <f>IF($B34="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C34,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="32">
         <f>IF($B35="","",IF($F35="Evitar","⚠ Conflito",IF(AND($F35="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B35))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
@@ -3326,7 +3333,7 @@
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Pesquisa feita em 04/09/2026, priorizando bulas oficiais (Anvisa), estudos revisados por pares (PubMed/PMC), órgãos de saúde do governo (NIH) e diretrizes de sociedades médicas (SBC, AHA, ACC/ESC, KDIGO, ESUR, ESVS, ADA/SBD). A coluna 'Área' diz se a fonte é sobre alimentação/interação com alimento ou sobre o quadro clínico em geral. Nenhuma destas fontes substitui a avaliação do seu médico — use como ponto de partida para perguntar e confirmar na consulta. Clique no link da coluna 'Fonte' para abrir a página original.</t>
         </is>
@@ -3365,667 +3372,667 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="32" t="n">
+      <c r="A4" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Suco de toranja em quantidade alta quase dobra o nível de Ticagrelor no sangue e aumenta seu efeito antiagregante</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Holmberg et al., 2013, Br J Clin Pharmacol (PubMed)</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Estudo clínico revisado por pares</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/23126367/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="32" t="n">
+      <c r="A5" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Bula brasileira do Brilinta (Ticagrelor) cita esse estudo e orienta evitar suco de toranja em grande quantidade</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Bula profissional Brilinta, AstraZeneca do Brasil (aprovada pela Anvisa)</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>Bula oficial (Anvisa)</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>https://www.azmed.com.br/content/dam/multibrand/br/pt/azmed-2022/home/bulas-profissionais/bulas/Brilinta_Bula_Profissional.pdf</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Enalapril (IECA) + sal light/suplemento de potássio aumenta risco de hipercalemia</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>StatPearls (NCBI Bookshelf), "Enalapril"</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Referência clínica revisada por pares</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>https://www.ncbi.nlm.nih.gov/books/NBK557708/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Álcool combinado com Aspirina aumenta o risco de sangramento gastrointestinal alto</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Kaufman et al., 1999, Ann Epidemiol (PubMed)</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>Estudo epidemiológico revisado por pares</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/10566713/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Arroz de levedura vermelha (red yeast rice) pode causar os mesmos efeitos colaterais e interações de uma estatina</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>NIH — National Center for Complementary and Integrative Health</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>Órgão oficial do governo dos EUA (NIH)</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F8" s="35" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>https://www.nccih.nih.gov/health/red-yeast-rice</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Rosuvastatina não tem interação relevante com toranja (via CYP2C9, diferente da via CYP3A4 usada pelo Ticagrelor)</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Bailey DG et al., 2013, CMAJ, "Grapefruit-medication interactions"</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Revisão científica revisada por pares</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3589309/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Duração de 12 meses de dupla antiagregação (Aspirina + Ticagrelor) após stent em síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>2016 ACC/AHA Guideline Focused Update on DAPT; reafirmado na diretriz ACS 2025 (JACC)</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedades médicas (ACC/AHA)</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F10" s="35" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>https://www.acc.org/latest-in-cardiology/ten-points-to-remember/2016/03/25/14/56/2016-acc-aha-guideline-focused-update-on-dapt</t>
         </is>
       </c>
     </row>
     <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="32" t="n">
+      <c r="A11" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Metas de LDL pós-infarto: &lt;50 mg/dL (SBC 2017); &lt;40 mg/dL na categoria "risco extremo" (SBC 2025, com critérios adicionais); &lt;55 mg/dL (ESC/EAS 2019 e ACC/AHA, risco muito alto)</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Diretriz Brasileira de Dislipidemias e Prevenção da Aterosclerose 2025 (SBC), Arq Bras Cardiol</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/tRJrwGzKX6C4GvMqdJpZcGk/?lang=pt</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="32" t="n">
+      <c r="A12" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Diretriz alimentar cardioprotetora: sódio controlado, gordura saturada &lt;6% das calorias, padrão Mediterrâneo/DASH</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>American Heart Association — AHA Diet and Lifestyle Recommendations / 2026 Dietary Guidance to Improve Cardiovascular Health (Circulation)</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (AHA)</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>https://www.heart.org/en/healthy-living/healthy-eating/eat-smart/nutrition-basics/aha-diet-and-lifestyle-recommendations</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>No Brasil, a Dieta Cardioprotetora Brasileira (DICA Br) aplica essas mesmas recomendações a alimentos típicos brasileiros</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>I Diretriz Brasileira de Prevenção Cardiovascular (SBC), Arq Bras Cardiol</t>
         </is>
       </c>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/X94tMKwdnBjkCzVKpXwBqmD/?lang=pt</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Critério objetivo de Lesão Renal Aguda (LRA) estágio 1: creatinina sobe ≥0,3 mg/dL em 48h</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>KDIGO — Clinical Practice Guideline for Acute Kidney Injury, 2012</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (KDIGO)</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>https://kdigo.org/wp-content/uploads/2016/10/KDIGO-2012-AKI-Guideline-English.pdf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Exame padrão para proteinúria é a relação albumina/creatinina urinária (ACR/RAC), categorias A1/A2/A3</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>KDIGO — Clinical Practice Guideline for CKD, 2012 (categorias mantidas na atualização 2024)</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (KDIGO)</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>https://kdigo.org/wp-content/uploads/2017/02/KDIGO_2012_CKD_GL.pdf</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Múltiplas exposições a contraste em dias próximos são fator de risco para lesão renal por contraste, com pico em 3-5 dias e resolução em 7-14 dias</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>ESUR — Post-contrast acute kidney injury, Guidelines v10.0, 2018</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESUR)</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>https://www.esur.org/wp-content/uploads/2022/03/ESUR-Guidelines-10_0-Final-Version.pdf</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Definição de infarto periprocedimento (tipo 4a): troponina &gt;5x o limite superior + evidência de nova isquemia</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Thygesen K, Alpert JS et al. — Fourth Universal Definition of Myocardial Infarction, 2018</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>Documento conjunto de sociedades médicas (ESC/ACC/AHA/WHF)</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F17" s="35" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000000617</t>
         </is>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="32" t="n">
+      <c r="A18" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Limiares de segurança para manter um IECA (Enalapril): potássio até 5,5 mmol/L e creatinina com alta até 50% (abaixo de 3 mg/dL) são toleráveis; reexame em 1-2 semanas</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>ESC — Guidelines for the diagnosis and treatment of acute and chronic heart failure, 2021</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC)</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F18" s="35" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/42/36/3599/6358045</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="32" t="n">
+      <c r="A19" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Reforço da duração de 12 meses de dupla antiagregação após síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>ESC — Guidelines for the management of acute coronary syndromes, 2023</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC)</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/45/14/1193/7516285</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Encaminhamento para reabilitação cardíaca antes da alta é recomendação Classe 1 (a mais forte) após síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>ACC/AHA/ACEP/NAEMSP/SCAI — Guideline for the Management of Patients With Acute Coronary Syndromes, 2025</t>
         </is>
       </c>
-      <c r="D20" s="33" t="inlineStr">
+      <c r="D20" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedades médicas (ACC/AHA e outras)</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F20" s="35" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000001309</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Estudo que sustenta a combinação estatina + ezetimiba para reduzir LDL após síndrome coronariana aguda (IMPROVE-IT)</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Cannon CP et al. — Ezetimibe Added to Statin Therapy after Acute Coronary Syndromes, N Engl J Med 2015</t>
         </is>
       </c>
-      <c r="D21" s="33" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>Estudo clínico revisado por pares</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F21" s="35" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>https://www.nejm.org/doi/full/10.1056/NEJMoa1410489</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="33" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>HbA1c ≥6,5% sugere diabetes prévio; abaixo de 5,7% (caso do paciente) é consistente com hiperglicemia de estresse, não diabetes</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>American Diabetes Association — Standards of Care in Diabetes, edições 2024-2026</t>
         </is>
       </c>
-      <c r="D22" s="33" t="inlineStr">
+      <c r="D22" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ADA)</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
         <is>
           <t>https://diabetesjournals.org/care/article/49/Supplement_1/S339/163925/16-Diabetes-Care-in-the-Hospital-Standards-of-Care</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Até 60% dos pacientes com hiperglicemia de estresse na internação desenvolvem diabetes em 6-12 meses</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Sociedade Brasileira de Diabetes — Hiperglicemia Hospitalar no Paciente Não-Crítico</t>
         </is>
       </c>
-      <c r="D23" s="33" t="inlineStr">
+      <c r="D23" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBD)</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F23" s="35" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>https://diretriz.diabetes.org.br/hiperglicemia-hospitalar-em-paciente-nao-critico/</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Placa carotídea com estenose abaixo de 50% é tratada de forma conservadora (antiagregante, estatina, controle de pressão), sem indicação de cirurgia</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>ESC/ESVS — Guidelines on Peripheral Arterial Diseases (2017/2018) e atualização sobre doença carotídea/vertebral (2023)</t>
         </is>
       </c>
-      <c r="D24" s="33" t="inlineStr">
+      <c r="D24" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC/ESVS)</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F24" s="35" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/39/9/763/4095038</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Mesma conduta conservadora para placa carotídea leve, do lado da prevenção de AVC</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>AHA/ASA — Guideline for the Prevention of Stroke in Patients With Stroke and TIA, 2021</t>
         </is>
       </c>
-      <c r="D25" s="33" t="inlineStr">
+      <c r="D25" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (AHA/ASA)</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F25" s="35" t="inlineStr">
+      <c r="F25" s="36" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/STR.0000000000000375</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Lista completa com os mesmos links (mais fácil de clicar em Markdown) também em referencia/historico-tratamento.md, seção 'Referências médicas'.</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -230,9 +230,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1267,11 +1264,7 @@
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>Bom</t>
-        </is>
-      </c>
+      <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="12" t="inlineStr">
         <is>
           <t>Mais açúcar que outras frutas</t>
@@ -1324,7 +1317,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2035,7 +2028,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2064,7 +2057,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2107,7 +2100,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2136,7 +2129,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2229,7 +2222,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2287,7 +2280,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2368,7 +2361,7 @@
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2424,41 +2417,41 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Escolha o alimento no menu suspenso da coluna 'Alimento' — a lista já vem filtrada por refeição (por isso não aparece arroz/feijão no café da manhã, por exemplo) e com os alimentos Liberados primeiro. Categoria, Porção sugerida e Classificação preenchem sozinhas. 'Sugestão' mostra um alimento que costuma combinar bem com o item escolhido logo acima (é uma dica, não é obrigatório escolher). Se 'Conflito' mostrar '⚠ Conflito', evite reunir esses itens na mesma refeição.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Legenda:</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>⚠ Conflito</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>CAFÉ DA MANHÃ</t>
         </is>
@@ -2472,181 +2465,181 @@
       <c r="H5" s="11" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="28">
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="30">
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G7" s="31" t="inlineStr"/>
-      <c r="H7" s="32">
+      <c r="G7" s="30" t="inlineStr"/>
+      <c r="H7" s="31">
         <f>IF($B7="","",IF($F7="Evitar","⚠ Conflito",IF(AND($F7="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B7))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="28">
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="30">
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="30">
         <f>IF($B7="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C7,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="31">
         <f>IF($B8="","",IF($F8="Evitar","⚠ Conflito",IF(AND($F8="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B8))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="28">
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="30">
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="30">
         <f>IF($B8="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C8,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="31">
         <f>IF($B9="","",IF($F9="Evitar","⚠ Conflito",IF(AND($F9="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B9))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="28">
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="30">
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="30">
         <f>IF($B9="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C9,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <f>IF($B10="","",IF($F10="Evitar","⚠ Conflito",IF(AND($F10="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B10))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="28">
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="30">
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="30">
         <f>IF($B10="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C10,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="31">
         <f>IF($B11="","",IF($F11="Evitar","⚠ Conflito",IF(AND($F11="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B11))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>ALMOÇO</t>
         </is>
@@ -2660,181 +2653,181 @@
       <c r="H13" s="11" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="28">
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="30">
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="31" t="inlineStr"/>
-      <c r="H15" s="32">
+      <c r="G15" s="30" t="inlineStr"/>
+      <c r="H15" s="31">
         <f>IF($B15="","",IF($F15="Evitar","⚠ Conflito",IF(AND($F15="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B15))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="28">
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="30">
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="30">
         <f>IF($B15="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C15,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="31">
         <f>IF($B16="","",IF($F16="Evitar","⚠ Conflito",IF(AND($F16="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B16))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="27" t="n"/>
-      <c r="C17" s="28">
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="30">
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <f>IF($B16="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C16,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="31">
         <f>IF($B17="","",IF($F17="Evitar","⚠ Conflito",IF(AND($F17="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B17))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="28">
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="30">
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="30">
         <f>IF($B17="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C17,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="31">
         <f>IF($B18="","",IF($F18="Evitar","⚠ Conflito",IF(AND($F18="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B18))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="27" t="n"/>
-      <c r="C19" s="28">
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="30">
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="30">
         <f>IF($B18="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C18,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="31">
         <f>IF($B19="","",IF($F19="Evitar","⚠ Conflito",IF(AND($F19="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B19))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>LANCHE</t>
         </is>
@@ -2848,181 +2841,181 @@
       <c r="H21" s="11" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G22" s="25" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="28">
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="30">
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="31" t="inlineStr"/>
-      <c r="H23" s="32">
+      <c r="G23" s="30" t="inlineStr"/>
+      <c r="H23" s="31">
         <f>IF($B23="","",IF($F23="Evitar","⚠ Conflito",IF(AND($F23="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B23))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="26" t="n">
+      <c r="A24" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="28">
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="30">
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="30">
         <f>IF($B23="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C23,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="31">
         <f>IF($B24="","",IF($F24="Evitar","⚠ Conflito",IF(AND($F24="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B24))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="26" t="n">
+      <c r="A25" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="27" t="n"/>
-      <c r="C25" s="28">
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="30">
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="30">
         <f>IF($B24="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C24,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="31">
         <f>IF($B25="","",IF($F25="Evitar","⚠ Conflito",IF(AND($F25="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B25))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="26" t="n">
+      <c r="A26" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="28">
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="30">
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="30">
         <f>IF($B25="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C25,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="31">
         <f>IF($B26="","",IF($F26="Evitar","⚠ Conflito",IF(AND($F26="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B26))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="27" t="n"/>
-      <c r="C27" s="28">
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="30">
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="30">
         <f>IF($B26="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C26,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="31">
         <f>IF($B27="","",IF($F27="Evitar","⚠ Conflito",IF(AND($F27="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B27))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>JANTAR</t>
         </is>
@@ -3036,175 +3029,175 @@
       <c r="H29" s="11" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G30" s="25" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H30" s="25" t="inlineStr">
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="26" t="n">
+      <c r="A31" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="27" t="n"/>
-      <c r="C31" s="28">
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="30">
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="31" t="inlineStr"/>
-      <c r="H31" s="32">
+      <c r="G31" s="30" t="inlineStr"/>
+      <c r="H31" s="31">
         <f>IF($B31="","",IF($F31="Evitar","⚠ Conflito",IF(AND($F31="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B31))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="26" t="n">
+      <c r="A32" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="28">
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="30">
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="30">
         <f>IF($B31="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C31,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="31">
         <f>IF($B32="","",IF($F32="Evitar","⚠ Conflito",IF(AND($F32="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B32))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="26" t="n">
+      <c r="A33" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="28">
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="30">
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="30">
         <f>IF($B32="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C32,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="31">
         <f>IF($B33="","",IF($F33="Evitar","⚠ Conflito",IF(AND($F33="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B33))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="26" t="n">
+      <c r="A34" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="28">
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="30">
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="30">
         <f>IF($B33="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C33,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="31">
         <f>IF($B34="","",IF($F34="Evitar","⚠ Conflito",IF(AND($F34="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B34))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="26" t="n">
+      <c r="A35" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="28">
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="27">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="30">
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="30">
         <f>IF($B34="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C34,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="31">
         <f>IF($B35="","",IF($F35="Evitar","⚠ Conflito",IF(AND($F35="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B35))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
@@ -3333,7 +3326,7 @@
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Pesquisa feita em 04/09/2026, priorizando bulas oficiais (Anvisa), estudos revisados por pares (PubMed/PMC), órgãos de saúde do governo (NIH) e diretrizes de sociedades médicas (SBC, AHA, ACC/ESC, KDIGO, ESUR, ESVS, ADA/SBD). A coluna 'Área' diz se a fonte é sobre alimentação/interação com alimento ou sobre o quadro clínico em geral. Nenhuma destas fontes substitui a avaliação do seu médico — use como ponto de partida para perguntar e confirmar na consulta. Clique no link da coluna 'Fonte' para abrir a página original.</t>
         </is>
@@ -3372,667 +3365,667 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="33" t="n">
+      <c r="A4" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Suco de toranja em quantidade alta quase dobra o nível de Ticagrelor no sangue e aumenta seu efeito antiagregante</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Holmberg et al., 2013, Br J Clin Pharmacol (PubMed)</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Estudo clínico revisado por pares</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/23126367/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Bula brasileira do Brilinta (Ticagrelor) cita esse estudo e orienta evitar suco de toranja em grande quantidade</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>Bula profissional Brilinta, AstraZeneca do Brasil (aprovada pela Anvisa)</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Bula oficial (Anvisa)</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>https://www.azmed.com.br/content/dam/multibrand/br/pt/azmed-2022/home/bulas-profissionais/bulas/Brilinta_Bula_Profissional.pdf</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Enalapril (IECA) + sal light/suplemento de potássio aumenta risco de hipercalemia</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>StatPearls (NCBI Bookshelf), "Enalapril"</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Referência clínica revisada por pares</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F6" s="36" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>https://www.ncbi.nlm.nih.gov/books/NBK557708/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Álcool combinado com Aspirina aumenta o risco de sangramento gastrointestinal alto</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>Kaufman et al., 1999, Ann Epidemiol (PubMed)</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>Estudo epidemiológico revisado por pares</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/10566713/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="33" t="n">
+      <c r="A8" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Arroz de levedura vermelha (red yeast rice) pode causar os mesmos efeitos colaterais e interações de uma estatina</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>NIH — National Center for Complementary and Integrative Health</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>Órgão oficial do governo dos EUA (NIH)</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F8" s="36" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>https://www.nccih.nih.gov/health/red-yeast-rice</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="33" t="n">
+      <c r="A9" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Rosuvastatina não tem interação relevante com toranja (via CYP2C9, diferente da via CYP3A4 usada pelo Ticagrelor)</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>Bailey DG et al., 2013, CMAJ, "Grapefruit-medication interactions"</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Revisão científica revisada por pares</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F9" s="36" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3589309/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="33" t="n">
+      <c r="A10" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Duração de 12 meses de dupla antiagregação (Aspirina + Ticagrelor) após stent em síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>2016 ACC/AHA Guideline Focused Update on DAPT; reafirmado na diretriz ACS 2025 (JACC)</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedades médicas (ACC/AHA)</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F10" s="36" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>https://www.acc.org/latest-in-cardiology/ten-points-to-remember/2016/03/25/14/56/2016-acc-aha-guideline-focused-update-on-dapt</t>
         </is>
       </c>
     </row>
     <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Metas de LDL pós-infarto: &lt;50 mg/dL (SBC 2017); &lt;40 mg/dL na categoria "risco extremo" (SBC 2025, com critérios adicionais); &lt;55 mg/dL (ESC/EAS 2019 e ACC/AHA, risco muito alto)</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>Diretriz Brasileira de Dislipidemias e Prevenção da Aterosclerose 2025 (SBC), Arq Bras Cardiol</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/tRJrwGzKX6C4GvMqdJpZcGk/?lang=pt</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Diretriz alimentar cardioprotetora: sódio controlado, gordura saturada &lt;6% das calorias, padrão Mediterrâneo/DASH</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>American Heart Association — AHA Diet and Lifestyle Recommendations / 2026 Dietary Guidance to Improve Cardiovascular Health (Circulation)</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (AHA)</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>https://www.heart.org/en/healthy-living/healthy-eating/eat-smart/nutrition-basics/aha-diet-and-lifestyle-recommendations</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="33" t="n">
+      <c r="A13" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>No Brasil, a Dieta Cardioprotetora Brasileira (DICA Br) aplica essas mesmas recomendações a alimentos típicos brasileiros</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>I Diretriz Brasileira de Prevenção Cardiovascular (SBC), Arq Bras Cardiol</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/X94tMKwdnBjkCzVKpXwBqmD/?lang=pt</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="33" t="n">
+      <c r="A14" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Critério objetivo de Lesão Renal Aguda (LRA) estágio 1: creatinina sobe ≥0,3 mg/dL em 48h</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>KDIGO — Clinical Practice Guideline for Acute Kidney Injury, 2012</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (KDIGO)</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>https://kdigo.org/wp-content/uploads/2016/10/KDIGO-2012-AKI-Guideline-English.pdf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="33" t="n">
+      <c r="A15" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Exame padrão para proteinúria é a relação albumina/creatinina urinária (ACR/RAC), categorias A1/A2/A3</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>KDIGO — Clinical Practice Guideline for CKD, 2012 (categorias mantidas na atualização 2024)</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (KDIGO)</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>https://kdigo.org/wp-content/uploads/2017/02/KDIGO_2012_CKD_GL.pdf</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="33" t="n">
+      <c r="A16" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Múltiplas exposições a contraste em dias próximos são fator de risco para lesão renal por contraste, com pico em 3-5 dias e resolução em 7-14 dias</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>ESUR — Post-contrast acute kidney injury, Guidelines v10.0, 2018</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESUR)</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F16" s="36" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>https://www.esur.org/wp-content/uploads/2022/03/ESUR-Guidelines-10_0-Final-Version.pdf</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="33" t="n">
+      <c r="A17" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Definição de infarto periprocedimento (tipo 4a): troponina &gt;5x o limite superior + evidência de nova isquemia</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Thygesen K, Alpert JS et al. — Fourth Universal Definition of Myocardial Infarction, 2018</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>Documento conjunto de sociedades médicas (ESC/ACC/AHA/WHF)</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr">
+      <c r="F17" s="35" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000000617</t>
         </is>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="33" t="n">
+      <c r="A18" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Limiares de segurança para manter um IECA (Enalapril): potássio até 5,5 mmol/L e creatinina com alta até 50% (abaixo de 3 mg/dL) são toleráveis; reexame em 1-2 semanas</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>ESC — Guidelines for the diagnosis and treatment of acute and chronic heart failure, 2021</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC)</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/42/36/3599/6358045</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="33" t="n">
+      <c r="A19" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Reforço da duração de 12 meses de dupla antiagregação após síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>ESC — Guidelines for the management of acute coronary syndromes, 2023</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC)</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/45/14/1193/7516285</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="33" t="n">
+      <c r="A20" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Encaminhamento para reabilitação cardíaca antes da alta é recomendação Classe 1 (a mais forte) após síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>ACC/AHA/ACEP/NAEMSP/SCAI — Guideline for the Management of Patients With Acute Coronary Syndromes, 2025</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedades médicas (ACC/AHA e outras)</t>
         </is>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F20" s="36" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000001309</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="33" t="n">
+      <c r="A21" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Estudo que sustenta a combinação estatina + ezetimiba para reduzir LDL após síndrome coronariana aguda (IMPROVE-IT)</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Cannon CP et al. — Ezetimibe Added to Statin Therapy after Acute Coronary Syndromes, N Engl J Med 2015</t>
         </is>
       </c>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>Estudo clínico revisado por pares</t>
         </is>
       </c>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F21" s="36" t="inlineStr">
+      <c r="F21" s="35" t="inlineStr">
         <is>
           <t>https://www.nejm.org/doi/full/10.1056/NEJMoa1410489</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="33" t="n">
+      <c r="A22" s="32" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>HbA1c ≥6,5% sugere diabetes prévio; abaixo de 5,7% (caso do paciente) é consistente com hiperglicemia de estresse, não diabetes</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>American Diabetes Association — Standards of Care in Diabetes, edições 2024-2026</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ADA)</t>
         </is>
       </c>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F22" s="36" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>https://diabetesjournals.org/care/article/49/Supplement_1/S339/163925/16-Diabetes-Care-in-the-Hospital-Standards-of-Care</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="33" t="n">
+      <c r="A23" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Até 60% dos pacientes com hiperglicemia de estresse na internação desenvolvem diabetes em 6-12 meses</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>Sociedade Brasileira de Diabetes — Hiperglicemia Hospitalar no Paciente Não-Crítico</t>
         </is>
       </c>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBD)</t>
         </is>
       </c>
-      <c r="E23" s="33" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F23" s="36" t="inlineStr">
+      <c r="F23" s="35" t="inlineStr">
         <is>
           <t>https://diretriz.diabetes.org.br/hiperglicemia-hospitalar-em-paciente-nao-critico/</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="33" t="n">
+      <c r="A24" s="32" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Placa carotídea com estenose abaixo de 50% é tratada de forma conservadora (antiagregante, estatina, controle de pressão), sem indicação de cirurgia</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>ESC/ESVS — Guidelines on Peripheral Arterial Diseases (2017/2018) e atualização sobre doença carotídea/vertebral (2023)</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC/ESVS)</t>
         </is>
       </c>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="E24" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/39/9/763/4095038</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="33" t="n">
+      <c r="A25" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Mesma conduta conservadora para placa carotídea leve, do lado da prevenção de AVC</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>AHA/ASA — Guideline for the Prevention of Stroke in Patients With Stroke and TIA, 2021</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (AHA/ASA)</t>
         </is>
       </c>
-      <c r="E25" s="33" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F25" s="36" t="inlineStr">
+      <c r="F25" s="35" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/STR.0000000000000375</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Lista completa com os mesmos links (mais fácil de clicar em Markdown) também em referencia/historico-tratamento.md, seção 'Referências médicas'.</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="64" customHeight="1">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr"/>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>150 g (6-8 fatias)</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
+          <t>1-2x/semana</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -1587,18 +1587,22 @@
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="12" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="78" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>8-10 peças (nigiri/hossomaki)</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1614,25 +1618,25 @@
       <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Preferir cortes magros</t>
+          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
+          <t>quase todo dia</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -1646,52 +1650,67 @@
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr"/>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Ovo</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>1 unidade</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>até 5x/semana</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Laticínios</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr"/>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 concha</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1707,72 +1726,49 @@
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="12" t="inlineStr"/>
     </row>
-    <row r="26" ht="50" customHeight="1">
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Queijo branco frescal</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>30 g</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Laticínios</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Leite desnatado</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr"/>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr"/>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="50" customHeight="1">
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Queijo frescal light</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Polenghi</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>30 g (1 fatia)</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
       <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
-        </is>
-      </c>
+      <c r="H27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="50" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr"/>
@@ -1783,36 +1779,40 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr"/>
+          <t>Queijo frescal light</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Polenghi</t>
+        </is>
+      </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -1823,155 +1823,159 @@
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Vigor</t>
-        </is>
-      </c>
+          <t>Mussarela</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr"/>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr"/>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="50" customHeight="1">
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Iogurte grego zero</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Vigor</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>90 g (1 pote)</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr"/>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr"/>
-      <c r="H33" s="12" t="inlineStr"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Refrigerante zero</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr"/>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr"/>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr"/>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
@@ -1985,7 +1989,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr"/>
@@ -1996,7 +2000,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
@@ -2007,86 +2011,97 @@
       <c r="G36" s="13" t="inlineStr"/>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="64" customHeight="1">
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr"/>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+      <c r="H37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr"/>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr"/>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Doces e Sobremesas</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr"/>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr"/>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr"/>
@@ -2108,165 +2123,150 @@
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Doces industrializados</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="inlineStr"/>
-      <c r="H41" s="12" t="inlineStr"/>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Doces e Sobremesas</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr"/>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr"/>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Gorduras e Temperos</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr"/>
+      <c r="H43" s="12" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr"/>
-      <c r="H44" s="12" t="inlineStr"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Manteiga</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr"/>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="inlineStr"/>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr"/>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr"/>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
+      <c r="H46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr"/>
@@ -2288,20 +2288,20 @@
       <c r="G47" s="13" t="inlineStr"/>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+          <t>Preferir azeite</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2309,32 +2309,51 @@
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr"/>
-      <c r="H48" s="12" t="inlineStr"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>Vegetais e Verduras</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="11" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="11" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr"/>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr"/>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Ervas e temperos naturais</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr"/>
@@ -2354,14 +2373,53 @@
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="11" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr"/>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr"/>
+      <c r="H52" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2371,18 +2429,18 @@
   <mergeCells count="11">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G25 G26 G27 G28 G29 G30 G31 G33 G34 G35 G36 G37 G38 G40 G41 G42 G44 G45 G46 G47 G48 G50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G27 G28 G29 G30 G31 G32 G33 G35 G36 G37 G38 G39 G40 G42 G43 G44 G46 G47 G48 G49 G50 G52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4071,7 +4129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4380,7 +4438,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -4390,7 +4448,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -4464,7 +4522,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -4474,7 +4532,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -4548,7 +4606,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -4558,7 +4616,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -4632,7 +4690,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -4642,7 +4700,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -4712,7 +4770,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -4722,7 +4780,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -4796,7 +4854,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -4806,7 +4864,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -4876,7 +4934,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Ervas e temperos naturais</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -4886,7 +4944,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Ervas e temperos naturais</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -4946,7 +5004,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Arroz branco</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -4956,7 +5014,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Arroz branco</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -5020,7 +5078,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Arroz branco</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -5030,7 +5088,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Arroz branco</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -5094,7 +5152,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -5104,7 +5162,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -5168,7 +5226,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -5178,7 +5236,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -5195,7 +5253,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5210,15 +5268,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>150 g (6-8 fatias)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>1-2x/semana</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
@@ -5238,7 +5300,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -5248,7 +5310,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -5265,7 +5327,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5280,7 +5342,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>8-10 peças (nigiri/hossomaki)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5290,7 +5352,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Preferir cortes magros</t>
+          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -5312,7 +5374,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -5322,7 +5384,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -5339,7 +5401,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5354,20 +5416,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
+          <t>quase todo dia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>X</t>
@@ -5386,7 +5444,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -5396,7 +5454,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5413,7 +5471,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5423,20 +5481,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
@@ -5454,9 +5516,19 @@
           <t>Uva</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>Mussarela</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5473,12 +5545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Laticínios</t>
+          <t>Proteínas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5488,12 +5560,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -5502,21 +5574,35 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>Manga</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5533,12 +5619,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Laticínios</t>
+          <t>Proteínas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5548,31 +5634,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>1 concha</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>Mussarela</t>
@@ -5597,7 +5679,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5612,19 +5694,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>X</t>
@@ -5661,7 +5739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5671,7 +5749,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5681,12 +5759,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5725,7 +5803,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5740,17 +5818,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5789,7 +5867,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5799,22 +5877,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5853,7 +5931,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5863,22 +5941,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5917,12 +5995,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5932,35 +6010,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>Manteiga</t>
@@ -5985,12 +6059,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6000,35 +6074,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>Vegetais e Verduras|Jantar</t>
@@ -6043,7 +6113,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6058,12 +6128,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2x/dia</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -6072,18 +6142,26 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6103,31 +6181,35 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6137,24 +6219,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>X</t>
@@ -6171,7 +6249,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6181,46 +6259,46 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6240,7 +6318,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -6248,31 +6326,23 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6290,20 +6360,28 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6313,117 +6391,125 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6433,24 +6519,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
@@ -6467,7 +6549,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6492,26 +6574,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6521,12 +6599,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -6534,7 +6612,11 @@
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
@@ -6551,50 +6633,134 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -230,6 +230,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -700,7 +703,7 @@
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cuidados na Alimentação — pós-infarto (25/08/2026)</t>
@@ -827,7 +830,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1">
+    <row r="12" ht="63.75" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Atenção especial — LDL</t>
@@ -851,7 +854,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
+    <row r="14" ht="49.5" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Medicações em uso (receita 03/09/2026)</t>
@@ -863,7 +866,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
+    <row r="15" ht="63.75" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Interação medicamentosa — Ticagrelor</t>
@@ -875,7 +878,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1">
+    <row r="16" ht="63.75" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Interação medicamentosa — Enalapril</t>
@@ -899,7 +902,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="50" customHeight="1">
+    <row r="18" ht="49.5" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Interação medicamentosa — Rosucor (estatina)</t>
@@ -911,7 +914,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="50" customHeight="1">
+    <row r="19" ht="49.5" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Reabilitação cardíaca</t>
@@ -956,7 +959,7 @@
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plano Geral — o que comer, inclusive fora de casa</t>
@@ -1061,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1071,17 +1074,17 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Alimentos e Quantidades — lista de referência</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Liberado</t>
@@ -1145,7 +1148,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="19.5" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Frutas</t>
@@ -1159,7 +1162,7 @@
       <c r="G4" s="11" t="n"/>
       <c r="H4" s="11" t="n"/>
     </row>
-    <row r="5" ht="50" customHeight="1">
+    <row r="5" ht="49.5" customHeight="1">
       <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Maçã fuji (com casca)</t>
@@ -1264,7 +1267,11 @@
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
           <t>Mais açúcar que outras frutas</t>
@@ -1300,7 +1307,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
+    <row r="10" ht="63.75" customHeight="1">
       <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Toranja / grapefruit</t>
@@ -1317,7 +1324,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -1329,7 +1336,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Grãos e Cereais</t>
@@ -1397,7 +1404,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
+    <row r="14" ht="49.5" customHeight="1">
       <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Aveia integral em flocos</t>
@@ -1455,7 +1462,7 @@
       <c r="G15" s="13" t="inlineStr"/>
       <c r="H15" s="12" t="inlineStr"/>
     </row>
-    <row r="16" ht="64" customHeight="1">
+    <row r="16" ht="63.75" customHeight="1">
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Pão francês integral (multigrãos)</t>
@@ -1488,7 +1495,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="148" customHeight="1">
+    <row r="17" ht="200.25" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Granola zero açúcar</t>
@@ -1521,7 +1528,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Proteínas</t>
@@ -1726,7 +1733,7 @@
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="12" t="inlineStr"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Laticínios</t>
@@ -1765,7 +1772,7 @@
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="12" t="inlineStr"/>
     </row>
-    <row r="28" ht="50" customHeight="1">
+    <row r="28" ht="49.5" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Queijo branco frescal</t>
@@ -1794,7 +1801,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="50" customHeight="1">
+    <row r="29" ht="49.5" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Queijo frescal light</t>
@@ -1827,7 +1834,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="50" customHeight="1">
+    <row r="30" ht="49.5" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Mussarela</t>
@@ -1885,7 +1892,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="50" customHeight="1">
+    <row r="32" ht="49.5" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Iogurte grego zero</t>
@@ -1947,7 +1954,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
@@ -2069,7 +2076,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="64" customHeight="1">
+    <row r="39" ht="63.75" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Suco de toranja / grapefruit</t>
@@ -2086,7 +2093,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2115,7 +2122,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2127,7 +2134,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
+    <row r="41" ht="19.5" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
@@ -2158,7 +2165,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2187,7 +2194,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2224,7 +2231,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
@@ -2280,7 +2287,7 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
@@ -2321,105 +2328,134 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="36" customHeight="1">
+    <row r="49" ht="78" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr"/>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr"/>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr"/>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr"/>
+      <c r="H51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr"/>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr"/>
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr"/>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr"/>
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2431,16 +2467,16 @@
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G27 G28 G29 G30 G31 G32 G33 G35 G36 G37 G38 G39 G40 G42 G43 G44 G46 G47 G48 G49 G50 G52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G27 G28 G29 G30 G31 G32 G33 G35 G36 G37 G38 G39 G40 G42 G43 G44 G46 G47 G48 G49 G50 G51 G53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2467,7 +2503,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Montar uma Refeição — escolha os alimentos de cada refeição</t>
@@ -2475,41 +2511,41 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Escolha o alimento no menu suspenso da coluna 'Alimento' — a lista já vem filtrada por refeição (por isso não aparece arroz/feijão no café da manhã, por exemplo) e com os alimentos Liberados primeiro. Categoria, Porção sugerida e Classificação preenchem sozinhas. 'Sugestão' mostra um alimento que costuma combinar bem com o item escolhido logo acima (é uma dica, não é obrigatório escolher). Se 'Conflito' mostrar '⚠ Conflito', evite reunir esses itens na mesma refeição.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Legenda:</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Evitar</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>⚠ Conflito</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>CAFÉ DA MANHÃ</t>
         </is>
@@ -2523,181 +2559,181 @@
       <c r="H5" s="11" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="n">
+    <row r="7" ht="25.5" customHeight="1">
+      <c r="A7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="26" t="n"/>
-      <c r="C7" s="27">
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E7" s="25" t="n"/>
-      <c r="F7" s="29">
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B7,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G7" s="30" t="inlineStr"/>
-      <c r="H7" s="31">
+      <c r="G7" s="31" t="inlineStr"/>
+      <c r="H7" s="32">
         <f>IF($B7="","",IF($F7="Evitar","⚠ Conflito",IF(AND($F7="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B7))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="25" t="n">
+    <row r="8" ht="25.5" customHeight="1">
+      <c r="A8" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="n"/>
-      <c r="C8" s="27">
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="29">
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B8,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <f>IF($B7="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C7,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>IF($B8="","",IF($F8="Evitar","⚠ Conflito",IF(AND($F8="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B8))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="n">
+    <row r="9" ht="25.5" customHeight="1">
+      <c r="A9" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="26" t="n"/>
-      <c r="C9" s="27">
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="29">
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B9,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>IF($B8="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C8,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>IF($B9="","",IF($F9="Evitar","⚠ Conflito",IF(AND($F9="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B9))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="n">
+    <row r="10" ht="25.5" customHeight="1">
+      <c r="A10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="27">
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="29">
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B10,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>IF($B9="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C9,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>IF($B10="","",IF($F10="Evitar","⚠ Conflito",IF(AND($F10="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B10))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="25" t="n">
+    <row r="11" ht="25.5" customHeight="1">
+      <c r="A11" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="27">
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="29">
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B11,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>IF($B10="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C10,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Café da manhã",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>IF($B11="","",IF($F11="Evitar","⚠ Conflito",IF(AND($F11="Moderar",SUMPRODUCT(($B$7:$B$11&lt;&gt;"")*(ROW($B$7:$B$11)&lt;&gt;ROW($B11))*(($F$7:$F$11="Moderar")+($F$7:$F$11="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>ALMOÇO</t>
         </is>
@@ -2711,181 +2747,181 @@
       <c r="H13" s="11" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="25" t="n">
+    <row r="15" ht="25.5" customHeight="1">
+      <c r="A15" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="27">
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="29">
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B15,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="30" t="inlineStr"/>
-      <c r="H15" s="31">
+      <c r="G15" s="31" t="inlineStr"/>
+      <c r="H15" s="32">
         <f>IF($B15="","",IF($F15="Evitar","⚠ Conflito",IF(AND($F15="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B15))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="25" t="n">
+    <row r="16" ht="25.5" customHeight="1">
+      <c r="A16" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="27">
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="29">
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B16,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <f>IF($B15="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C15,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>IF($B16="","",IF($F16="Evitar","⚠ Conflito",IF(AND($F16="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B16))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="25" t="n">
+    <row r="17" ht="25.5" customHeight="1">
+      <c r="A17" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="27">
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="29">
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B17,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>IF($B16="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C16,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>IF($B17="","",IF($F17="Evitar","⚠ Conflito",IF(AND($F17="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B17))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="25" t="n">
+    <row r="18" ht="25.5" customHeight="1">
+      <c r="A18" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="27">
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="29">
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B18,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="31">
         <f>IF($B17="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C17,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="32">
         <f>IF($B18="","",IF($F18="Evitar","⚠ Conflito",IF(AND($F18="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B18))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="25" t="n">
+    <row r="19" ht="25.5" customHeight="1">
+      <c r="A19" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="27">
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="29">
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B19,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="31">
         <f>IF($B18="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C18,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Almoço",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="32">
         <f>IF($B19="","",IF($F19="Evitar","⚠ Conflito",IF(AND($F19="Moderar",SUMPRODUCT(($B$15:$B$19&lt;&gt;"")*(ROW($B$15:$B$19)&lt;&gt;ROW($B19))*(($F$15:$F$19="Moderar")+($F$15:$F$19="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>LANCHE</t>
         </is>
@@ -2899,181 +2935,181 @@
       <c r="H21" s="11" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G22" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H22" s="24" t="inlineStr">
+      <c r="H22" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="25" t="n">
+    <row r="23" ht="25.5" customHeight="1">
+      <c r="A23" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="27">
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="29">
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B23,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="30" t="inlineStr"/>
-      <c r="H23" s="31">
+      <c r="G23" s="31" t="inlineStr"/>
+      <c r="H23" s="32">
         <f>IF($B23="","",IF($F23="Evitar","⚠ Conflito",IF(AND($F23="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B23))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="25" t="n">
+    <row r="24" ht="25.5" customHeight="1">
+      <c r="A24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="27">
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="29">
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B24,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <f>IF($B23="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C23,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <f>IF($B24="","",IF($F24="Evitar","⚠ Conflito",IF(AND($F24="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B24))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="25" t="n">
+    <row r="25" ht="25.5" customHeight="1">
+      <c r="A25" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="26" t="n"/>
-      <c r="C25" s="27">
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="29">
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B25,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <f>IF($B24="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C24,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <f>IF($B25="","",IF($F25="Evitar","⚠ Conflito",IF(AND($F25="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B25))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="25" t="n">
+    <row r="26" ht="25.5" customHeight="1">
+      <c r="A26" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="27">
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="29">
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B26,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="31">
         <f>IF($B25="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C25,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="32">
         <f>IF($B26="","",IF($F26="Evitar","⚠ Conflito",IF(AND($F26="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B26))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="25" t="n">
+    <row r="27" ht="25.5" customHeight="1">
+      <c r="A27" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="27">
+      <c r="B27" s="27" t="n"/>
+      <c r="C27" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="29">
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B27,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <f>IF($B26="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C26,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Lanche",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <f>IF($B27="","",IF($F27="Evitar","⚠ Conflito",IF(AND($F27="Moderar",SUMPRODUCT(($B$23:$B$27&lt;&gt;"")*(ROW($B$23:$B$27)&lt;&gt;ROW($B27))*(($F$23:$F$27="Moderar")+($F$23:$F$27="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>JANTAR</t>
         </is>
@@ -3087,180 +3123,180 @@
       <c r="H29" s="11" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>Alimento</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>Porção sugerida</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="25" t="inlineStr">
         <is>
           <t>Quantidade a comer</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F30" s="25" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G30" s="25" t="inlineStr">
         <is>
           <t>Sugestão (com base no item anterior)</t>
         </is>
       </c>
-      <c r="H30" s="24" t="inlineStr">
+      <c r="H30" s="25" t="inlineStr">
         <is>
           <t>Conflito</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="25" t="n">
+    <row r="31" ht="25.5" customHeight="1">
+      <c r="A31" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="27">
+      <c r="B31" s="27" t="n"/>
+      <c r="C31" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="29">
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B31,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="30" t="inlineStr"/>
-      <c r="H31" s="31">
+      <c r="G31" s="31" t="inlineStr"/>
+      <c r="H31" s="32">
         <f>IF($B31="","",IF($F31="Evitar","⚠ Conflito",IF(AND($F31="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B31))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="25" t="n">
+    <row r="32" ht="25.5" customHeight="1">
+      <c r="A32" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="27">
+      <c r="B32" s="27" t="n"/>
+      <c r="C32" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="29">
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B32,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="31">
         <f>IF($B31="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C31,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H32" s="31">
+      <c r="H32" s="32">
         <f>IF($B32="","",IF($F32="Evitar","⚠ Conflito",IF(AND($F32="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B32))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="25" t="n">
+    <row r="33" ht="25.5" customHeight="1">
+      <c r="A33" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="27">
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="25" t="n"/>
-      <c r="F33" s="29">
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B33,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="31">
         <f>IF($B32="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C32,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="32">
         <f>IF($B33="","",IF($F33="Evitar","⚠ Conflito",IF(AND($F33="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B33))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="25" t="n">
+    <row r="34" ht="25.5" customHeight="1">
+      <c r="A34" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="27">
+      <c r="B34" s="27" t="n"/>
+      <c r="C34" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="29">
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B34,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="31">
         <f>IF($B33="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C33,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="32">
         <f>IF($B34="","",IF($F34="Evitar","⚠ Conflito",IF(AND($F34="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B34))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="25" t="n">
+    <row r="35" ht="25.5" customHeight="1">
+      <c r="A35" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B35" s="26" t="n"/>
-      <c r="C35" s="27">
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="28">
         <f>IFERROR(INDEX(Ref_Alimentos!$B$2:$B$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="29">
         <f>IFERROR(INDEX(Ref_Alimentos!$D$2:$D$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="25" t="n"/>
-      <c r="F35" s="29">
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="30">
         <f>IFERROR(INDEX(Ref_Alimentos!$C$2:$C$101,MATCH($B35,Ref_Alimentos!$A$2:$A$101,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="31">
         <f>IF($B34="","",IFERROR(INDEX(Ref_Alimentos!$R$2:$R$60,MATCH(IFERROR(INDEX(Ref_Alimentos!$U$2:$U$9,MATCH($C34,Ref_Alimentos!$T$2:$T$9,0)),"")&amp;"|"&amp;"Jantar",Ref_Alimentos!$Q$2:$Q$60,0)),""))</f>
         <v/>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="32">
         <f>IF($B35="","",IF($F35="Evitar","⚠ Conflito",IF(AND($F35="Moderar",SUMPRODUCT(($B$31:$B$35&lt;&gt;"")*(ROW($B$31:$B$35)&lt;&gt;ROW($B35))*(($F$31:$F$35="Moderar")+($F$31:$F$35="Evitar")))&gt;0),"⚠ Conflito","")))</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="44" customHeight="1">
+    <row r="37" ht="43.5" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Limitações conhecidas: a ordem do menu suspenso é fixa (Liberado &gt; Moderar &gt; Evitar), ela não se reordena sozinha conforme o item anterior — quem indica o que combina melhor é a coluna 'Sugestão'. A coluna 'Conflito' é uma aproximação (marca um item 'Evitar' sozinho, ou dois itens 'Moderar'/'Evitar' juntos na mesma refeição) — não é uma checagem real de interação entre os dois alimentos específicos.</t>
@@ -3376,15 +3412,15 @@
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fontes e Referências — de onde vieram as informações médicas</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="2" ht="55.5" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Pesquisa feita em 04/09/2026, priorizando bulas oficiais (Anvisa), estudos revisados por pares (PubMed/PMC), órgãos de saúde do governo (NIH) e diretrizes de sociedades médicas (SBC, AHA, ACC/ESC, KDIGO, ESUR, ESVS, ADA/SBD). A coluna 'Área' diz se a fonte é sobre alimentação/interação com alimento ou sobre o quadro clínico em geral. Nenhuma destas fontes substitui a avaliação do seu médico — use como ponto de partida para perguntar e confirmar na consulta. Clique no link da coluna 'Fonte' para abrir a página original.</t>
         </is>
@@ -3423,667 +3459,667 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="32" t="n">
+      <c r="A4" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Suco de toranja em quantidade alta quase dobra o nível de Ticagrelor no sangue e aumenta seu efeito antiagregante</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Holmberg et al., 2013, Br J Clin Pharmacol (PubMed)</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Estudo clínico revisado por pares</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/23126367/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="32" t="n">
+      <c r="A5" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Bula brasileira do Brilinta (Ticagrelor) cita esse estudo e orienta evitar suco de toranja em grande quantidade</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Bula profissional Brilinta, AstraZeneca do Brasil (aprovada pela Anvisa)</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>Bula oficial (Anvisa)</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>https://www.azmed.com.br/content/dam/multibrand/br/pt/azmed-2022/home/bulas-profissionais/bulas/Brilinta_Bula_Profissional.pdf</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Enalapril (IECA) + sal light/suplemento de potássio aumenta risco de hipercalemia</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>StatPearls (NCBI Bookshelf), "Enalapril"</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Referência clínica revisada por pares</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>https://www.ncbi.nlm.nih.gov/books/NBK557708/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Álcool combinado com Aspirina aumenta o risco de sangramento gastrointestinal alto</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Kaufman et al., 1999, Ann Epidemiol (PubMed)</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>Estudo epidemiológico revisado por pares</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/10566713/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Arroz de levedura vermelha (red yeast rice) pode causar os mesmos efeitos colaterais e interações de uma estatina</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>NIH — National Center for Complementary and Integrative Health</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>Órgão oficial do governo dos EUA (NIH)</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F8" s="35" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>https://www.nccih.nih.gov/health/red-yeast-rice</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Rosuvastatina não tem interação relevante com toranja (via CYP2C9, diferente da via CYP3A4 usada pelo Ticagrelor)</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Bailey DG et al., 2013, CMAJ, "Grapefruit-medication interactions"</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Revisão científica revisada por pares</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3589309/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Duração de 12 meses de dupla antiagregação (Aspirina + Ticagrelor) após stent em síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>2016 ACC/AHA Guideline Focused Update on DAPT; reafirmado na diretriz ACS 2025 (JACC)</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedades médicas (ACC/AHA)</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F10" s="35" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>https://www.acc.org/latest-in-cardiology/ten-points-to-remember/2016/03/25/14/56/2016-acc-aha-guideline-focused-update-on-dapt</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="32" t="n">
+    <row r="11" ht="49.5" customHeight="1">
+      <c r="A11" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Metas de LDL pós-infarto: &lt;50 mg/dL (SBC 2017); &lt;40 mg/dL na categoria "risco extremo" (SBC 2025, com critérios adicionais); &lt;55 mg/dL (ESC/EAS 2019 e ACC/AHA, risco muito alto)</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Diretriz Brasileira de Dislipidemias e Prevenção da Aterosclerose 2025 (SBC), Arq Bras Cardiol</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/tRJrwGzKX6C4GvMqdJpZcGk/?lang=pt</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="32" t="n">
+    <row r="12" ht="49.5" customHeight="1">
+      <c r="A12" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Diretriz alimentar cardioprotetora: sódio controlado, gordura saturada &lt;6% das calorias, padrão Mediterrâneo/DASH</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>American Heart Association — AHA Diet and Lifestyle Recommendations / 2026 Dietary Guidance to Improve Cardiovascular Health (Circulation)</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (AHA)</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>https://www.heart.org/en/healthy-living/healthy-eating/eat-smart/nutrition-basics/aha-diet-and-lifestyle-recommendations</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>No Brasil, a Dieta Cardioprotetora Brasileira (DICA Br) aplica essas mesmas recomendações a alimentos típicos brasileiros</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>I Diretriz Brasileira de Prevenção Cardiovascular (SBC), Arq Bras Cardiol</t>
         </is>
       </c>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBC)</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>https://www.scielo.br/j/abc/a/X94tMKwdnBjkCzVKpXwBqmD/?lang=pt</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Critério objetivo de Lesão Renal Aguda (LRA) estágio 1: creatinina sobe ≥0,3 mg/dL em 48h</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>KDIGO — Clinical Practice Guideline for Acute Kidney Injury, 2012</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (KDIGO)</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>https://kdigo.org/wp-content/uploads/2016/10/KDIGO-2012-AKI-Guideline-English.pdf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Exame padrão para proteinúria é a relação albumina/creatinina urinária (ACR/RAC), categorias A1/A2/A3</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>KDIGO — Clinical Practice Guideline for CKD, 2012 (categorias mantidas na atualização 2024)</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (KDIGO)</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>https://kdigo.org/wp-content/uploads/2017/02/KDIGO_2012_CKD_GL.pdf</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Múltiplas exposições a contraste em dias próximos são fator de risco para lesão renal por contraste, com pico em 3-5 dias e resolução em 7-14 dias</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>ESUR — Post-contrast acute kidney injury, Guidelines v10.0, 2018</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESUR)</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>https://www.esur.org/wp-content/uploads/2022/03/ESUR-Guidelines-10_0-Final-Version.pdf</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Definição de infarto periprocedimento (tipo 4a): troponina &gt;5x o limite superior + evidência de nova isquemia</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Thygesen K, Alpert JS et al. — Fourth Universal Definition of Myocardial Infarction, 2018</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>Documento conjunto de sociedades médicas (ESC/ACC/AHA/WHF)</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F17" s="35" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000000617</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="32" t="n">
+    <row r="18" ht="49.5" customHeight="1">
+      <c r="A18" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Limiares de segurança para manter um IECA (Enalapril): potássio até 5,5 mmol/L e creatinina com alta até 50% (abaixo de 3 mg/dL) são toleráveis; reexame em 1-2 semanas</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>ESC — Guidelines for the diagnosis and treatment of acute and chronic heart failure, 2021</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC)</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F18" s="35" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/42/36/3599/6358045</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="32" t="n">
+      <c r="A19" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Reforço da duração de 12 meses de dupla antiagregação após síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>ESC — Guidelines for the management of acute coronary syndromes, 2023</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC)</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/45/14/1193/7516285</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Encaminhamento para reabilitação cardíaca antes da alta é recomendação Classe 1 (a mais forte) após síndrome coronariana aguda</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>ACC/AHA/ACEP/NAEMSP/SCAI — Guideline for the Management of Patients With Acute Coronary Syndromes, 2025</t>
         </is>
       </c>
-      <c r="D20" s="33" t="inlineStr">
+      <c r="D20" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedades médicas (ACC/AHA e outras)</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F20" s="35" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/CIR.0000000000001309</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Estudo que sustenta a combinação estatina + ezetimiba para reduzir LDL após síndrome coronariana aguda (IMPROVE-IT)</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Cannon CP et al. — Ezetimibe Added to Statin Therapy after Acute Coronary Syndromes, N Engl J Med 2015</t>
         </is>
       </c>
-      <c r="D21" s="33" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>Estudo clínico revisado por pares</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="F21" s="35" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>https://www.nejm.org/doi/full/10.1056/NEJMoa1410489</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="33" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>HbA1c ≥6,5% sugere diabetes prévio; abaixo de 5,7% (caso do paciente) é consistente com hiperglicemia de estresse, não diabetes</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>American Diabetes Association — Standards of Care in Diabetes, edições 2024-2026</t>
         </is>
       </c>
-      <c r="D22" s="33" t="inlineStr">
+      <c r="D22" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ADA)</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
         <is>
           <t>https://diabetesjournals.org/care/article/49/Supplement_1/S339/163925/16-Diabetes-Care-in-the-Hospital-Standards-of-Care</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Até 60% dos pacientes com hiperglicemia de estresse na internação desenvolvem diabetes em 6-12 meses</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Sociedade Brasileira de Diabetes — Hiperglicemia Hospitalar no Paciente Não-Crítico</t>
         </is>
       </c>
-      <c r="D23" s="33" t="inlineStr">
+      <c r="D23" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (SBD)</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F23" s="35" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>https://diretriz.diabetes.org.br/hiperglicemia-hospitalar-em-paciente-nao-critico/</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Placa carotídea com estenose abaixo de 50% é tratada de forma conservadora (antiagregante, estatina, controle de pressão), sem indicação de cirurgia</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>ESC/ESVS — Guidelines on Peripheral Arterial Diseases (2017/2018) e atualização sobre doença carotídea/vertebral (2023)</t>
         </is>
       </c>
-      <c r="D24" s="33" t="inlineStr">
+      <c r="D24" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (ESC/ESVS)</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F24" s="35" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>https://academic.oup.com/eurheartj/article/39/9/763/4095038</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Mesma conduta conservadora para placa carotídea leve, do lado da prevenção de AVC</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>AHA/ASA — Guideline for the Prevention of Stroke in Patients With Stroke and TIA, 2021</t>
         </is>
       </c>
-      <c r="D25" s="33" t="inlineStr">
+      <c r="D25" s="34" t="inlineStr">
         <is>
           <t>Diretriz de sociedade médica (AHA/ASA)</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>Clínico geral</t>
         </is>
       </c>
-      <c r="F25" s="35" t="inlineStr">
+      <c r="F25" s="36" t="inlineStr">
         <is>
           <t>https://www.ahajournals.org/doi/10.1161/STR.0000000000000375</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Lista completa com os mesmos links (mais fácil de clicar em Markdown) também em referencia/historico-tratamento.md, seção 'Referências médicas'.</t>
         </is>
@@ -4129,7 +4165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4790,7 +4826,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -4934,7 +4970,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -4944,7 +4980,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -5004,7 +5040,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Ervas e temperos naturais</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -5014,7 +5050,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Ervas e temperos naturais</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -5078,7 +5114,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Arroz branco</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -5088,7 +5124,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Arroz branco</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -5152,7 +5188,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Arroz branco</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -5162,7 +5198,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Arroz branco</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -5226,7 +5262,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -5236,7 +5272,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -5300,17 +5336,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -5374,17 +5410,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -5439,22 +5475,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5513,22 +5549,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5587,22 +5623,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5657,12 +5693,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5717,22 +5763,22 @@
       <c r="J21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Vegetais e Verduras|Lanche</t>
+          <t>Gorduras e Temperos|Lanche</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
     </row>
@@ -5781,22 +5827,22 @@
       <c r="J22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>Suco natural sem açúcar</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Chocolate amargo (70%+)</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Grãos e Cereais|Jantar</t>
+          <t>Vegetais e Verduras|Lanche</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Arroz integral</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
     </row>
@@ -5845,22 +5891,22 @@
       <c r="J23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Proteínas|Jantar</t>
+          <t>Grãos e Cereais|Jantar</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Arroz integral</t>
         </is>
       </c>
     </row>
@@ -5909,22 +5955,22 @@
       <c r="J24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Bebidas|Jantar</t>
+          <t>Proteínas|Jantar</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Peixe</t>
         </is>
       </c>
     </row>
@@ -5973,22 +6019,22 @@
       <c r="J25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas|Jantar</t>
+          <t>Bebidas|Jantar</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
@@ -6037,22 +6083,22 @@
       <c r="J26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos|Jantar</t>
+          <t>Doces e Sobremesas|Jantar</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
     </row>
@@ -6099,14 +6145,24 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Vegetais e Verduras|Jantar</t>
+          <t>Gorduras e Temperos|Jantar</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
     </row>
@@ -6155,6 +6211,16 @@
       <c r="J28" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras|Jantar</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6699,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6643,31 +6709,39 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>X</t>
@@ -6677,7 +6751,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6687,20 +6761,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
@@ -6717,50 +6795,90 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1064,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1733,60 +1733,64 @@
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="12" t="inlineStr"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26" ht="106" customHeight="1">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Kare (curry japonês) com lombo de porco</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr"/>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr"/>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Laticínios</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Leite desnatado</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr"/>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28" ht="49.5" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr"/>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -1795,26 +1799,18 @@
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr"/>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+      <c r="H28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="49.5" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Polenghi</t>
-        </is>
-      </c>
+          <t>Queijo branco frescal</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr"/>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1830,82 +1826,82 @@
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="49.5" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Mussarela</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr"/>
+          <t>Queijo frescal light</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Polenghi</t>
+        </is>
+      </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49.5" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr"/>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="49.5" customHeight="1">
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Vigor</t>
-        </is>
-      </c>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr"/>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1921,194 +1917,198 @@
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="49.5" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Requeijão</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr"/>
+          <t>Iogurte grego zero</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Vigor</t>
+        </is>
+      </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="12" t="inlineStr">
         <is>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr"/>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (≈15 g)</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
           <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr"/>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr"/>
-      <c r="H35" s="12" t="inlineStr"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr"/>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr"/>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H36" s="12" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr"/>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr"/>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr"/>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr"/>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="63.75" customHeight="1">
+      <c r="H38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr"/>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr"/>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="63.75" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr"/>
@@ -2130,57 +2130,57 @@
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="12" t="inlineStr">
         <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr"/>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr"/>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr"/>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr"/>
@@ -2200,262 +2200,291 @@
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr"/>
-      <c r="H43" s="12" t="inlineStr"/>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr"/>
+      <c r="H44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr"/>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="F45" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr"/>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr"/>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G46" s="13" t="inlineStr"/>
-      <c r="H46" s="12" t="inlineStr"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr"/>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H47" s="12" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr"/>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="78" customHeight="1">
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr"/>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr"/>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="78" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr"/>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr"/>
       <c r="D51" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr"/>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr"/>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="F52" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr"/>
-      <c r="H51" s="12" t="inlineStr"/>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr"/>
+      <c r="H52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="11" t="n"/>
-      <c r="G52" s="11" t="n"/>
-      <c r="H52" s="11" t="n"/>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr"/>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr"/>
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr"/>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr"/>
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="18" t="inlineStr">
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2465,18 +2494,18 @@
   <mergeCells count="11">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G27 G28 G29 G30 G31 G32 G33 G35 G36 G37 G38 G39 G40 G42 G43 G44 G46 G47 G48 G49 G50 G51 G53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G26 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G43 G44 G45 G47 G48 G49 G50 G51 G52 G54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4165,7 +4194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5410,7 +5439,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Kare (curry japonês) com lombo de porco</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -5420,7 +5449,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Kare (curry japonês) com lombo de porco</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -5480,7 +5509,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -5490,7 +5519,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5554,7 +5583,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -5564,7 +5593,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5628,7 +5657,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -5638,7 +5667,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5698,7 +5727,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -5708,7 +5737,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5725,50 +5754,64 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Kare (curry japonês) com lombo de porco</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Laticínios</t>
+          <t>Proteínas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>Mussarela</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>Refrigerante zero</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5785,7 +5828,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5800,19 +5843,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>X</t>
@@ -5849,7 +5888,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5864,7 +5903,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5874,7 +5913,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5913,7 +5952,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5923,22 +5962,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5977,7 +6016,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5987,22 +6026,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -6041,7 +6080,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6056,7 +6095,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6066,7 +6105,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -6105,7 +6144,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6115,22 +6154,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -6169,50 +6208,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>Vegetais e Verduras|Jantar</t>
@@ -6227,7 +6262,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6237,25 +6272,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>X</t>
@@ -6275,7 +6310,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6285,37 +6320,45 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6325,24 +6368,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>X</t>
@@ -6359,7 +6398,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6369,22 +6408,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -6403,7 +6442,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6428,31 +6467,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6472,24 +6511,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>X</t>
@@ -6499,7 +6530,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6522,20 +6553,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6545,24 +6592,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
@@ -6575,47 +6618,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6625,37 +6668,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6665,41 +6708,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6709,39 +6748,31 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>X</t>
@@ -6751,7 +6782,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6761,31 +6792,39 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>X</t>
@@ -6795,7 +6834,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6805,20 +6844,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
@@ -6835,50 +6878,90 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1064,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1983,161 +1983,165 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="35" ht="134" customHeight="1">
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Cream cheese light</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (30 g)</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr"/>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr"/>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr"/>
-      <c r="H36" s="12" t="inlineStr"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr"/>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr"/>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr"/>
-      <c r="H38" s="12" t="inlineStr"/>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr"/>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="63.75" customHeight="1">
+      <c r="H39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr"/>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="63.75" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr"/>
@@ -2159,57 +2163,57 @@
       <c r="G41" s="13" t="inlineStr"/>
       <c r="H41" s="12" t="inlineStr">
         <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr"/>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr"/>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="11" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="inlineStr"/>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr"/>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr"/>
@@ -2229,262 +2233,603 @@
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr"/>
-      <c r="H44" s="12" t="inlineStr"/>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr"/>
       <c r="D45" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr"/>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G45" s="13" t="inlineStr"/>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr"/>
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr"/>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G47" s="13" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr"/>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H48" s="12" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr"/>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr"/>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="78" customHeight="1">
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr"/>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="78" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr"/>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr"/>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr"/>
       <c r="D52" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr"/>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr"/>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr"/>
-      <c r="H52" s="12" t="inlineStr"/>
-    </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr"/>
+      <c r="H53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="11" t="n"/>
-      <c r="G53" s="11" t="n"/>
-      <c r="H53" s="11" t="n"/>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr"/>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr"/>
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr"/>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr"/>
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Brócolis</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr"/>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr"/>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Couve</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr"/>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr"/>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Espinafre</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr"/>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr"/>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr"/>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr"/>
+      <c r="H59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Cenoura</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr"/>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr"/>
+      <c r="H60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Abobrinha</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr"/>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr"/>
+      <c r="H61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Beterraba</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr"/>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr"/>
+      <c r="H62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr"/>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr"/>
+      <c r="H63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Pepino</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr"/>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr"/>
+      <c r="H64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Berinjela</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr"/>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="inlineStr"/>
+      <c r="H65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Pimentão</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr"/>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="inlineStr"/>
+      <c r="H66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Repolho</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr"/>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr"/>
+      <c r="H67" s="12" t="inlineStr"/>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2494,18 +2839,18 @@
   <mergeCells count="11">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G26 G28 G29 G30 G31 G32 G33 G34 G36 G37 G38 G39 G40 G41 G43 G44 G45 G47 G48 G49 G50 G51 G52 G54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G26 G28 G29 G30 G31 G32 G33 G34 G35 G37 G38 G39 G40 G41 G42 G44 G45 G46 G48 G49 G50 G51 G52 G53 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4194,7 +4539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5217,7 +5562,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Arroz branco</t>
+          <t>Brócolis</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -5227,7 +5572,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Arroz branco</t>
+          <t>Brócolis</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -5291,7 +5636,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Couve</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -5301,7 +5646,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Couve</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -5365,7 +5710,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Espinafre</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -5375,7 +5720,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Espinafre</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -5439,7 +5784,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -5449,7 +5794,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -5509,17 +5854,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5583,17 +5928,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Abobrinha</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Abobrinha</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -5652,22 +5997,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Beterraba</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Beterraba</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -5722,22 +6067,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5796,22 +6141,22 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5866,12 +6211,22 @@
       <c r="J22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Berinjela</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Uva</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Berinjela</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -5930,12 +6285,22 @@
       <c r="J23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Manga</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5994,12 +6359,22 @@
       <c r="J24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Cream cheese light</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Repolho</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Mussarela</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Repolho</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -6058,12 +6433,22 @@
       <c r="J25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Arroz branco</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Arroz branco</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -6122,12 +6507,22 @@
       <c r="J26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Cream cheese light</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -6186,12 +6581,22 @@
       <c r="J27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Refrigerante zero</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -6248,6 +6653,26 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Kare (curry japonês) com lombo de porco</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Suco natural sem açúcar</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Kare (curry japonês) com lombo de porco</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>Vegetais e Verduras|Jantar</t>
@@ -6262,55 +6687,71 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Cream cheese light</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (30 g)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Refrigerante zero</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Refrigerante zero</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6320,25 +6761,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>X</t>
@@ -6352,13 +6793,28 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sal</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6368,37 +6824,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Suco de toranja / grapefruit</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6408,24 +6887,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>X</t>
@@ -6438,11 +6913,26 @@
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Açúcar refinado</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6452,22 +6942,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -6482,11 +6972,26 @@
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6511,31 +7016,31 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6555,24 +7060,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>X</t>
@@ -6582,7 +7079,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6605,20 +7102,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6628,24 +7141,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
@@ -6658,47 +7167,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6708,37 +7217,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6748,41 +7257,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6792,39 +7297,31 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>X</t>
@@ -6834,7 +7331,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6844,31 +7341,39 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>X</t>
@@ -6878,7 +7383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6888,20 +7393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
@@ -6918,50 +7427,606 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gorduras e Temperos</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Vegetais e verduras em geral</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Brócolis</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Couve</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Espinafre</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cenoura</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Abobrinha</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Beterraba</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pepino</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Berinjela</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Pimentão</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Repolho</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1064,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1495,97 +1495,101 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="200.25" customHeight="1">
+    <row r="17" ht="92" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Granola zero açúcar</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Castanha do Bem</t>
+          <t>Rap10</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>20 g (1 colher de sopa)</t>
+          <t>1 unidade (33 g)</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr"/>
       <c r="H17" s="12" t="inlineStr">
         <is>
+          <t>Rótulo real (porção 40 g ≈ 1 unidade): 120 kcal, 170 mg de sódio, 1,6 g de gordura saturada, 1,2 g de fibras, 0 g de gordura trans, pouco açúcar adicionado (0,3 g). Sódio e gordura saturada acima do que se espera de uma tortilha simples — moderar a frequência e, se possível, somar com o restante do sódio do dia. Contém glúten (triticale). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="200.25" customHeight="1">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Granola zero açúcar</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Castanha do Bem</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>20 g (1 colher de sopa)</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
           <t>Rótulo real (porção 20 g): 83 kcal, 2,8 g de gordura (0,9 g saturada), 12 g de carboidrato, 1,1 g de açúcar (zero adicionado, adoçada com esteviol), 3 g de proteína, 2 g de fibra e 19 mg de sódio. Feita com aveia, coco, amêndoa, castanha de caju, castanha do pará e uva-passa — sem açúcar refinado, mas é calórica (415 kcal/100 g) e tem gordura saturada das castanhas/coco: manter na porção indicada, sem repetir a colher. Contém glúten; rótulo declara conter lactose (apesar de não haver laticínio nos ingredientes — provavelmente contaminação cruzada declarada); pode conter amendoim, avelã, centeio, leite, macadâmia, nozes, ovos, pecã, soja e trigo.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Proteínas</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Peixe</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr"/>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>150 g</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr"/>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>150 g (6-8 fatias)</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>1-2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -1596,68 +1600,72 @@
       <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="78" customHeight="1">
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>8-10 peças (nigiri/hossomaki)</t>
+          <t>150 g (6-8 fatias)</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1-2x/semana</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="78" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>8-10 peças (nigiri/hossomaki)</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="12" t="inlineStr"/>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr"/>
@@ -1668,61 +1676,61 @@
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+      <c r="H23" s="12" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr"/>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="12" t="inlineStr"/>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr"/>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1733,89 +1741,89 @@
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="12" t="inlineStr"/>
     </row>
-    <row r="26" ht="106" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr"/>
       <c r="D26" s="13" t="inlineStr">
         <is>
+          <t>1 concha</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr"/>
+      <c r="H26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27" ht="106" customHeight="1">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Kare (curry japonês) com lombo de porco</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr"/>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
           <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>1x/semana</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr"/>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Laticínios</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Leite desnatado</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr"/>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr"/>
-      <c r="H28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29" ht="49.5" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr"/>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -1824,26 +1832,18 @@
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr"/>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+      <c r="H29" s="12" t="inlineStr"/>
     </row>
     <row r="30" ht="49.5" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Polenghi</t>
-        </is>
-      </c>
+          <t>Queijo branco frescal</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr"/>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1859,82 +1859,82 @@
       <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="49.5" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Mussarela</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr"/>
+          <t>Queijo frescal light</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Polenghi</t>
+        </is>
+      </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="49.5" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr"/>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="49.5" customHeight="1">
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Vigor</t>
-        </is>
-      </c>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1950,53 +1950,53 @@
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="49.5" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Requeijão</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr"/>
+          <t>Iogurte grego zero</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Vigor</t>
+        </is>
+      </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr"/>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="134" customHeight="1">
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr"/>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (30 g)</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -2012,165 +2012,169 @@
       <c r="G35" s="13" t="inlineStr"/>
       <c r="H35" s="12" t="inlineStr">
         <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="134" customHeight="1">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Cream cheese light</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (30 g)</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr"/>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
           <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr"/>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G37" s="13" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr"/>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr"/>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H38" s="12" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr"/>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr"/>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr"/>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr"/>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="63.75" customHeight="1">
+      <c r="H40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr"/>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr"/>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="63.75" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr"/>
@@ -2192,57 +2196,57 @@
       <c r="G42" s="13" t="inlineStr"/>
       <c r="H42" s="12" t="inlineStr">
         <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr"/>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="inlineStr"/>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="inlineStr"/>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr"/>
@@ -2262,264 +2266,264 @@
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr"/>
-      <c r="H45" s="12" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr"/>
       <c r="D46" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr"/>
+      <c r="H46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr"/>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr"/>
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr"/>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="inlineStr"/>
-      <c r="H48" s="12" t="inlineStr"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr"/>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr"/>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H49" s="12" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F50" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr"/>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="78" customHeight="1">
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr"/>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr"/>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="78" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr"/>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr"/>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr"/>
       <c r="D53" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="inlineStr"/>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr"/>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr"/>
-      <c r="H53" s="12" t="inlineStr"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr"/>
+      <c r="H54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
-      <c r="C54" s="11" t="n"/>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="11" t="n"/>
-      <c r="G54" s="11" t="n"/>
-      <c r="H54" s="11" t="n"/>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>Vegetais e verduras em geral</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr"/>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G55" s="13" t="inlineStr"/>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
-        </is>
-      </c>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="11" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="11" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>Brócolis</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr"/>
@@ -2541,14 +2545,14 @@
       <c r="G56" s="13" t="inlineStr"/>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
+          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Couve</t>
+          <t>Brócolis</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr"/>
@@ -2570,14 +2574,14 @@
       <c r="G57" s="13" t="inlineStr"/>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Espinafre</t>
+          <t>Couve</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr"/>
@@ -2603,10 +2607,10 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
+    <row r="59" ht="36" customHeight="1">
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Espinafre</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr"/>
@@ -2626,12 +2630,16 @@
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr"/>
-      <c r="H59" s="12" t="inlineStr"/>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Cenoura</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr"/>
@@ -2656,7 +2664,7 @@
     <row r="61" ht="30" customHeight="1">
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Abobrinha</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr"/>
@@ -2681,7 +2689,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>Beterraba</t>
+          <t>Abobrinha</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr"/>
@@ -2692,7 +2700,7 @@
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -2706,7 +2714,7 @@
     <row r="63" ht="30" customHeight="1">
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Alface e folhas verdes (rúcula, agrião)</t>
+          <t>Beterraba</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr"/>
@@ -2717,7 +2725,7 @@
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -2731,7 +2739,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>Pepino</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr"/>
@@ -2756,7 +2764,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Berinjela</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr"/>
@@ -2767,7 +2775,7 @@
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F65" s="14" t="inlineStr">
@@ -2781,7 +2789,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>Pimentão</t>
+          <t>Berinjela</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr"/>
@@ -2792,7 +2800,7 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -2806,7 +2814,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Repolho</t>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr"/>
@@ -2828,8 +2836,33 @@
       <c r="G67" s="13" t="inlineStr"/>
       <c r="H67" s="12" t="inlineStr"/>
     </row>
-    <row r="69" ht="36" customHeight="1">
-      <c r="A69" s="18" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Repolho</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr"/>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr"/>
+      <c r="H68" s="12" t="inlineStr"/>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2837,20 +2870,20 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G19 G20 G21 G22 G23 G24 G25 G26 G28 G29 G30 G31 G32 G33 G34 G35 G37 G38 G39 G40 G41 G42 G44 G45 G46 G48 G49 G50 G51 G52 G53 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G18 G20 G21 G22 G23 G24 G25 G26 G27 G29 G30 G31 G32 G33 G34 G35 G36 G38 G39 G40 G41 G42 G43 G45 G46 G47 G49 G50 G51 G52 G53 G54 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4539,7 +4572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5515,7 +5548,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Granola zero açúcar</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5525,22 +5558,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20 g (1 colher de sopa)</t>
+          <t>1 unidade (33 g)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rótulo real (porção 20 g): 83 kcal, 2,8 g de gordura (0,9 g saturada), 12 g de carboidrato, 1,1 g de açúcar (zero adicionado, adoçada com esteviol), 3 g de proteína, 2 g de fibra e 19 mg de sódio. Feita com aveia, coco, amêndoa, castanha de caju, castanha do pará e uva-passa — sem açúcar refinado, mas é calórica (415 kcal/100 g) e tem gordura saturada das castanhas/coco: manter na porção indicada, sem repetir a colher. Contém glúten; rótulo declara conter lactose (apesar de não haver laticínio nos ingredientes — provavelmente contaminação cruzada declarada); pode conter amendoim, avelã, centeio, leite, macadâmia, nozes, ovos, pecã, soja e trigo.</t>
+          <t>Rótulo real (porção 40 g ≈ 1 unidade): 120 kcal, 170 mg de sódio, 1,6 g de gordura saturada, 1,2 g de fibras, 0 g de gordura trans, pouco açúcar adicionado (0,3 g). Sódio e gordura saturada acima do que se espera de uma tortilha simples — moderar a frequência e, se possível, somar com o restante do sódio do dia. Contém glúten (triticale). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5548,13 +5581,21 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Iogurte natural (desnatado, sem açúcar)</t>
@@ -5589,12 +5630,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Granola zero açúcar</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Proteínas</t>
+          <t>Grãos e Cereais</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5604,31 +5645,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>20 g (1 colher de sopa)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Rótulo real (porção 20 g): 83 kcal, 2,8 g de gordura (0,9 g saturada), 12 g de carboidrato, 1,1 g de açúcar (zero adicionado, adoçada com esteviol), 3 g de proteína, 2 g de fibra e 19 mg de sódio. Feita com aveia, coco, amêndoa, castanha de caju, castanha do pará e uva-passa — sem açúcar refinado, mas é calórica (415 kcal/100 g) e tem gordura saturada das castanhas/coco: manter na porção indicada, sem repetir a colher. Contém glúten; rótulo declara conter lactose (apesar de não haver laticínio nos ingredientes — provavelmente contaminação cruzada declarada); pode conter amendoim, avelã, centeio, leite, macadâmia, nozes, ovos, pecã, soja e trigo.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>Iogurte grego zero</t>
@@ -5663,7 +5704,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sashimi de salmão</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5678,17 +5719,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>150 g (6-8 fatias)</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1-2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Fonte de ômega-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -5737,7 +5778,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5747,22 +5788,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8-10 peças (nigiri/hossomaki)</t>
+          <t>150 g (6-8 fatias)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1x/semana</t>
+          <t>1-2x/semana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -5811,7 +5852,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5821,20 +5862,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>8-10 peças (nigiri/hossomaki)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
@@ -5881,7 +5926,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5891,7 +5936,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5901,14 +5946,10 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
@@ -5955,7 +5996,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5965,25 +6006,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>X</t>
@@ -6029,7 +6070,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6044,16 +6085,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>X</t>
@@ -6099,7 +6144,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6109,24 +6154,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
+          <t>1 concha</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
@@ -6173,45 +6214,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Kare (curry japonês) com lombo de porco</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Laticínios</t>
+          <t>Proteínas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -6243,7 +6288,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6258,19 +6303,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>X</t>
@@ -6285,7 +6326,7 @@
       <c r="J23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -6317,7 +6358,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6332,7 +6373,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -6342,7 +6383,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6359,7 +6400,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -6369,7 +6410,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -6391,7 +6432,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6401,22 +6442,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -6433,7 +6474,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Cream cheese light</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -6443,7 +6484,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -6465,7 +6506,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6475,22 +6516,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -6507,22 +6548,22 @@
       <c r="J26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -6539,7 +6580,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6554,7 +6595,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6564,7 +6605,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -6581,22 +6622,22 @@
       <c r="J27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Cream cheese light</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -6613,7 +6654,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6623,22 +6664,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -6655,22 +6696,22 @@
       <c r="J28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -6687,7 +6728,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6702,7 +6743,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1 colher de sopa (30 g)</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6712,7 +6753,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -6729,92 +6770,93 @@
       <c r="J29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Kare (curry japonês) com lombo de porco</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Kare (curry japonês) com lombo de porco</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Cream cheese light</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (30 g)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="J30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6824,25 +6866,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>X</t>
@@ -6860,24 +6902,24 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Sal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6887,52 +6929,60 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6942,24 +6992,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>X</t>
@@ -6974,24 +7020,24 @@
       <c r="J33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7001,22 +7047,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7031,11 +7077,26 @@
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7060,31 +7121,31 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7104,24 +7165,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>X</t>
@@ -7131,7 +7184,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7154,20 +7207,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7177,24 +7246,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
@@ -7207,47 +7272,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7257,37 +7322,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7297,41 +7362,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7341,39 +7402,31 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>X</t>
@@ -7383,7 +7436,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7393,31 +7446,39 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>X</t>
@@ -7427,7 +7488,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7437,20 +7498,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
@@ -7467,12 +7532,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Ervas e temperos naturais</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vegetais e Verduras</t>
+          <t>Gorduras e Temperos</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7490,26 +7555,14 @@
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>X</t>
@@ -7519,7 +7572,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brócolis</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7544,16 +7597,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>X</t>
@@ -7563,7 +7624,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Couve</t>
+          <t>Brócolis</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7588,7 +7649,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -7607,7 +7668,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Espinafre</t>
+          <t>Couve</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7651,7 +7712,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Espinafre</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7674,22 +7735,18 @@
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>X</t>
@@ -7699,7 +7756,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cenoura</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7723,7 +7780,11 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>X</t>
@@ -7743,7 +7804,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Abobrinha</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7773,7 +7834,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>X</t>
@@ -7783,7 +7848,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Beterraba</t>
+          <t>Abobrinha</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7803,7 +7868,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -7823,7 +7888,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alface e folhas verdes (rúcula, agrião)</t>
+          <t>Beterraba</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7843,7 +7908,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -7853,11 +7918,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>X</t>
@@ -7867,7 +7928,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pepino</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7911,7 +7972,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Berinjela</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7931,7 +7992,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -7941,7 +8002,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>X</t>
@@ -7951,7 +8016,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pimentão</t>
+          <t>Berinjela</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7971,7 +8036,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -7981,11 +8046,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>X</t>
@@ -7995,7 +8056,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Repolho</t>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8025,8 +8086,52 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Repolho</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1064,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1561,64 +1561,68 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19" ht="162" customHeight="1">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Granola zero açúcar</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Mãe Terra</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>20 g (1 colher de sopa)</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>Rótulo real (a porção do rótulo é 40 g/½ xícara; valores abaixo recalculados para 20 g, para manter a mesma porção das demais granolas da planilha): ~91 kcal, 3,6 g de gordura (0,7 g saturada, 0 g trans), 12 g de carboidrato, 0,3 g de açúcar total e zero adicionado (adoçada com eritritol, maltitol e glicosídeos de esteviol — polióis, geralmente bem tolerados nessa quantidade), 2,2 g de proteína, 1,6 g de fibra, só 1,3 mg de sódio (praticamente sem sódio). Leva castanha-do-pará, castanha-de-caju, coco e óleo vegetal — por isso é calórica e tem gordura saturada relevante mesmo sendo zero açúcar: manter a porção, sem repetir a colher. Contém glúten (aveia, flocos de trigo); pode conter diversos alérgenos por contaminação cruzada (amendoim, leite, castanhas variadas, soja).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Proteínas</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Peixe</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr"/>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>150 g</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="64" customHeight="1">
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>150 g (6-8 fatias)</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>1-2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1629,68 +1633,72 @@
       <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="78" customHeight="1">
+          <t>Fonte de ômega-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>8-10 peças (nigiri/hossomaki)</t>
+          <t>150 g (6-8 fatias)</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1-2x/semana</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr"/>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="78" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr"/>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>8-10 peças (nigiri/hossomaki)</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr"/>
@@ -1701,61 +1709,61 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+      <c r="H24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr"/>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="12" t="inlineStr"/>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr"/>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -1766,89 +1774,89 @@
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="12" t="inlineStr"/>
     </row>
-    <row r="27" ht="106" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr"/>
       <c r="D27" s="13" t="inlineStr">
         <is>
+          <t>1 concha</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28" ht="106" customHeight="1">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Kare (curry japonês) com lombo de porco</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr"/>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
           <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>1x/semana</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr"/>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Laticínios</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Leite desnatado</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr"/>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr"/>
-      <c r="H29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30" ht="49.5" customHeight="1">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr"/>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -1857,26 +1865,18 @@
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr"/>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+      <c r="H30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="49.5" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Polenghi</t>
-        </is>
-      </c>
+          <t>Queijo branco frescal</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr"/>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1892,82 +1892,82 @@
       <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="49.5" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Mussarela</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr"/>
+          <t>Queijo frescal light</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Polenghi</t>
+        </is>
+      </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="49.5" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="49.5" customHeight="1">
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Vigor</t>
-        </is>
-      </c>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr"/>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1983,53 +1983,53 @@
       <c r="G34" s="13" t="inlineStr"/>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="49.5" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Requeijão</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr"/>
+          <t>Iogurte grego zero</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Vigor</t>
+        </is>
+      </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr"/>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="134" customHeight="1">
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
+          <t>Requeijão</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr"/>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>1 colher de sopa (30 g)</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -2045,165 +2045,169 @@
       <c r="G36" s="13" t="inlineStr"/>
       <c r="H36" s="12" t="inlineStr">
         <is>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="134" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Cream cheese light</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>1 colher de sopa (30 g)</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr"/>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
           <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Bebidas</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>Água</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr"/>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="inlineStr"/>
-      <c r="H38" s="12" t="inlineStr"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr"/>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+      <c r="H39" s="12" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr"/>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr"/>
-      <c r="H40" s="12" t="inlineStr"/>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr"/>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr"/>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="63.75" customHeight="1">
+      <c r="H41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr"/>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr"/>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="63.75" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr"/>
@@ -2225,57 +2229,57 @@
       <c r="G43" s="13" t="inlineStr"/>
       <c r="H43" s="12" t="inlineStr">
         <is>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Bebida alcoólica</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr"/>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
           <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Doces e Sobremesas</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Açúcar refinado</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr"/>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="inlineStr"/>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr"/>
@@ -2295,264 +2299,264 @@
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr"/>
-      <c r="H46" s="12" t="inlineStr"/>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr"/>
       <c r="D47" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr"/>
+      <c r="H47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Chocolate amargo (70%+)</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr"/>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
           <t>10 g</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>2x/semana</t>
         </is>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>Moderar</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr"/>
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>Gorduras e Temperos</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>Azeite de oliva extra virgem</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr"/>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>1-2 colheres de sopa</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="inlineStr"/>
-      <c r="H49" s="12" t="inlineStr"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
+      <c r="H50" s="12" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr"/>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>Moderar</t>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr"/>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="78" customHeight="1">
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr"/>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr"/>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="78" customHeight="1">
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr"/>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>Evitar</t>
+          <t>3x/semana</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr"/>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr"/>
       <c r="D54" s="13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr"/>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Ervas e temperos naturais</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr"/>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
           <t>à vontade</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>Liberado</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr"/>
-      <c r="H54" s="12" t="inlineStr"/>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr"/>
+      <c r="H55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Vegetais e Verduras</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="11" t="n"/>
-      <c r="G55" s="11" t="n"/>
-      <c r="H55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>Vegetais e verduras em geral</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr"/>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>à vontade</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
-      </c>
-      <c r="G56" s="13" t="inlineStr"/>
-      <c r="H56" s="12" t="inlineStr">
-        <is>
-          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
-        </is>
-      </c>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="11" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Brócolis</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr"/>
@@ -2574,14 +2578,14 @@
       <c r="G57" s="13" t="inlineStr"/>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
+          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Couve</t>
+          <t>Brócolis</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr"/>
@@ -2603,14 +2607,14 @@
       <c r="G58" s="13" t="inlineStr"/>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Espinafre</t>
+          <t>Couve</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr"/>
@@ -2636,10 +2640,10 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
+    <row r="60" ht="36" customHeight="1">
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Espinafre</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr"/>
@@ -2659,12 +2663,16 @@
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr"/>
-      <c r="H60" s="12" t="inlineStr"/>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Cenoura</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr"/>
@@ -2689,7 +2697,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>Abobrinha</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr"/>
@@ -2714,7 +2722,7 @@
     <row r="63" ht="30" customHeight="1">
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Beterraba</t>
+          <t>Abobrinha</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr"/>
@@ -2725,7 +2733,7 @@
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -2739,7 +2747,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>Alface e folhas verdes (rúcula, agrião)</t>
+          <t>Beterraba</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr"/>
@@ -2750,7 +2758,7 @@
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -2764,7 +2772,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Pepino</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr"/>
@@ -2789,7 +2797,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>Berinjela</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr"/>
@@ -2800,7 +2808,7 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -2814,7 +2822,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Pimentão</t>
+          <t>Berinjela</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr"/>
@@ -2825,7 +2833,7 @@
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -2839,7 +2847,7 @@
     <row r="68" ht="30" customHeight="1">
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>Repolho</t>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr"/>
@@ -2861,8 +2869,33 @@
       <c r="G68" s="13" t="inlineStr"/>
       <c r="H68" s="12" t="inlineStr"/>
     </row>
-    <row r="70" ht="36" customHeight="1">
-      <c r="A70" s="18" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Repolho</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr"/>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr"/>
+      <c r="H69" s="12" t="inlineStr"/>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>Lista com os alimentos acrescentados até agora — não é uma lista completa. Use a skill 'adicionar-alimento' (ex.: "adicione sucrilhos") para ir acrescentando novos itens aos poucos. A coluna 'Gostoso' é sua — escolha do menu suspenso; o valor é preservado mesmo quando a planilha é regenerada por um alimento novo.</t>
         </is>
@@ -2870,20 +2903,20 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G18 G20 G21 G22 G23 G24 G25 G26 G27 G29 G30 G31 G32 G33 G34 G35 G36 G38 G39 G40 G41 G42 G43 G45 G46 G47 G49 G50 G51 G52 G53 G54 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14 G15 G16 G17 G18 G19 G21 G22 G23 G24 G25 G26 G27 G28 G30 G31 G32 G33 G34 G35 G36 G37 G39 G40 G41 G42 G43 G44 G46 G47 G48 G50 G51 G52 G53 G54 G55 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da lista" error="Escolha uma opção do menu (ou deixe em branco)." type="list" errorStyle="warning">
       <formula1>"Ruim,Normal,Bom,Muito bom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4572,7 +4605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5218,7 +5251,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Granola zero açúcar</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -5292,7 +5325,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Granola zero açúcar</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5302,7 +5335,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -5372,7 +5405,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5382,7 +5415,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -5442,7 +5475,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5452,7 +5485,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5516,7 +5549,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5526,7 +5559,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5598,7 +5631,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5608,7 +5641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5672,7 +5705,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5682,7 +5715,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -5704,12 +5737,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Granola zero açúcar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Proteínas</t>
+          <t>Grãos e Cereais</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5719,34 +5752,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>20 g (1 colher de sopa)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fonte de ômega-3</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Rótulo real (a porção do rótulo é 40 g/½ xícara; valores abaixo recalculados para 20 g, para manter a mesma porção das demais granolas da planilha): ~91 kcal, 3,6 g de gordura (0,7 g saturada, 0 g trans), 12 g de carboidrato, 0,3 g de açúcar total e zero adicionado (adoçada com eritritol, maltitol e glicosídeos de esteviol — polióis, geralmente bem tolerados nessa quantidade), 2,2 g de proteína, 1,6 g de fibra, só 1,3 mg de sódio (praticamente sem sódio). Leva castanha-do-pará, castanha-de-caju, coco e óleo vegetal — por isso é calórica e tem gordura saturada relevante mesmo sendo zero açúcar: manter a porção, sem repetir a colher. Contém glúten (aveia, flocos de trigo); pode conter diversos alérgenos por contaminação cruzada (amendoim, leite, castanhas variadas, soja).</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5756,7 +5789,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -5778,7 +5811,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sashimi de salmão</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5793,17 +5826,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>150 g (6-8 fatias)</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1-2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Fonte de ômega-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -5820,7 +5853,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5830,7 +5863,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5852,7 +5885,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sushi de salmão</t>
+          <t>Sashimi de salmão</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5862,22 +5895,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8-10 peças (nigiri/hossomaki)</t>
+          <t>150 g (6-8 fatias)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1x/semana</t>
+          <t>1-2x/semana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Peixe cru, sem arroz — mesma fonte de ômega-3 do peixe grelhado, conta na mesma cota semanal de peixe. Cuidado é só com o shoyu (molho de soja) do acompanhamento, rico em sódio: usar pouco. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -5894,7 +5927,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5904,7 +5937,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5926,7 +5959,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Frango sem pele</t>
+          <t>Sushi de salmão</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5936,20 +5969,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>8-10 peças (nigiri/hossomaki)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>quase todo dia</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Além do peixe, leva arroz temperado com açúcar/vinagre — mais carboidrato e um pouco de açúcar adicionado que o sashimi puro. Evitar versões com tempurá, cream cheese ou molhos cremosos/apimentados (mais gordura, sódio e calorias); usar pouco shoyu (sódio). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
@@ -5964,7 +6001,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -5974,7 +6011,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Cenoura</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -5996,7 +6033,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Carne vermelha magra</t>
+          <t>Frango sem pele</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6006,7 +6043,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6016,14 +6053,10 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Preferir cortes magros</t>
-        </is>
-      </c>
+          <t>quase todo dia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
@@ -6038,7 +6071,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -6048,7 +6081,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Alface e folhas verdes (rúcula, agrião)</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -6070,7 +6103,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovo</t>
+          <t>Carne vermelha magra</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6080,25 +6113,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>até 5x/semana</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Preferir cortes magros</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>X</t>
@@ -6112,7 +6145,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -6122,7 +6155,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Pepino</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -6144,7 +6177,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Feijão / leguminosas</t>
+          <t>Ovo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6159,16 +6192,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1 concha</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>até 5x/semana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>X</t>
@@ -6182,7 +6219,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -6192,7 +6229,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Pimentão</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -6214,7 +6251,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kare (curry japonês) com lombo de porco</t>
+          <t>Feijão / leguminosas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6224,24 +6261,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
+          <t>1 concha</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1x/semana</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
@@ -6256,7 +6289,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Tortilha</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -6266,7 +6299,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -6288,45 +6321,49 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Leite desnatado</t>
+          <t>Kare (curry japonês) com lombo de porco</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Laticínios</t>
+          <t>Proteínas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 concha (150-200 g do preparo, sem contar o arroz)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>1x/semana</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>O tablete de curry (roux) pronto costuma ser rico em sódio e conter gordura saturada (geralmente óleo de palma) na sua composição, além de ser espessado com farinha de trigo — é o principal ponto de atenção do prato, não o lombo suíno (corte magro) nem os vegetais (batata, cenoura, cebola). Preferir marcas com menos sódio por porção, se o rótulo estiver disponível. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -6336,7 +6373,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Manga</t>
+          <t>Uva</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -6358,7 +6395,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Queijo branco frescal</t>
+          <t>Leite desnatado</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6373,19 +6410,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>X</t>
@@ -6400,7 +6433,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -6410,7 +6443,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tortilha</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -6432,7 +6465,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Queijo frescal light</t>
+          <t>Queijo branco frescal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6447,7 +6480,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30 g (1 fatia)</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6457,7 +6490,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
+          <t>Tipo fresco (ex.: Minas frescal), sem cura/salga pesada — bem menos sódio e gordura que queijos curados. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -6474,7 +6507,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -6484,7 +6517,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Tortilha</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -6506,7 +6539,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mussarela</t>
+          <t>Queijo frescal light</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6516,22 +6549,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30 g</t>
+          <t>30 g (1 fatia)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 41 kcal e 105 mg de sódio por porção (bem abaixo de queijos comuns), 1,5 g de gordura saturada, sem açúcar adicionado. Contém lactose; sem glúten; pode conter soja.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -6548,7 +6581,7 @@
       <c r="J26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Cream cheese light</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -6558,7 +6591,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -6580,7 +6613,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Iogurte natural (desnatado, sem açúcar)</t>
+          <t>Mussarela</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6590,22 +6623,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1 unidade</t>
+          <t>30 g</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1x/dia</t>
+          <t>2x/semana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Prefira sempre a versão sem açúcar adicionado</t>
+          <t>Mais gordura saturada e sódio que o queijo branco frescal; prefira o frescal no dia a dia. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -6622,7 +6655,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -6632,7 +6665,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -6654,7 +6687,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Iogurte grego zero</t>
+          <t>Iogurte natural (desnatado, sem açúcar)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6669,7 +6702,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>90 g (1 pote)</t>
+          <t>1 unidade</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6679,7 +6712,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
+          <t>Prefira sempre a versão sem açúcar adicionado</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -6696,7 +6729,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -6706,7 +6739,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Cream cheese light</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -6728,7 +6761,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Requeijão</t>
+          <t>Iogurte grego zero</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6738,22 +6771,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1 colher de sopa (≈15 g)</t>
+          <t>90 g (1 pote)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2x/semana</t>
+          <t>1x/dia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: 50 kcal, 6,8 g de proteína (bem mais que iogurte comum), 0,2 g de gordura, 51 mg de sódio, zero adição de açúcar/gordura, sem lactose. Contém edulcorantes (sucralose e ciclamato).</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -6770,7 +6803,7 @@
       <c r="J29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -6780,7 +6813,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -6792,7 +6825,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cream cheese light</t>
+          <t>Requeijão</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6807,7 +6840,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1 colher de sopa (30 g)</t>
+          <t>1 colher de sopa (≈15 g)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6817,7 +6850,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rico em gordura saturada e sódio; prefira a versão light. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -6834,7 +6867,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -6844,7 +6877,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -6856,48 +6889,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Cream cheese light</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Laticínios</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>1 colher de sopa (30 g)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rótulo real (30 g): 63 kcal, 3,5 g de gordura saturada e 0,1 g de gordura trans (mesmo sendo 'light', é bastante gordura saturada para uma porção — quase 30% do limite diário recomendado num plano de 2000 kcal), 115 mg de sódio, 1,1 g de açúcar (sem açúcar adicionado). Ingredientes: leite integral, creme de leite, leite em pó desnatado, sal, fermento lático, espessantes (goma jataí, carragena), conservador sorbato de potássio (não é o mesmo que sal light/cloreto de potássio — sem interação com o Enalapril). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="J31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -6907,7 +6941,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Toranja / grapefruit</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -6919,7 +6953,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Refrigerante zero</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6929,25 +6963,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>à vontade</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>X</t>
@@ -6970,7 +7004,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Toranja / grapefruit</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -6982,7 +7016,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Café sem açúcar</t>
+          <t>Refrigerante zero</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6992,32 +7026,40 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1 xícara</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2x/dia</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Açúcar refinado</t>
@@ -7025,7 +7067,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -7037,7 +7079,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Suco natural sem açúcar</t>
+          <t>Café sem açúcar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7047,24 +7089,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1 xícara</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3x/semana</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Preferir a fruta inteira, que tem mais fibra</t>
-        </is>
-      </c>
+          <t>2x/dia</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>X</t>
@@ -7084,7 +7122,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -7096,7 +7134,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Suco de toranja / grapefruit</t>
+          <t>Suco natural sem açúcar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7106,22 +7144,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+          <t>Preferir a fruta inteira, que tem mais fibra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7136,11 +7174,16 @@
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Doces industrializados</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bebida alcoólica</t>
+          <t>Suco de toranja / grapefruit</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7165,31 +7208,31 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Interage com o Ticagrelor (estudo mostrou quase o dobro do nível do remédio no sangue); a bula diz que não é esperado ser clinicamente relevante p/ a maioria, mas orienta evitar — mais seguro evitar, já que você toma 2 antiagregantes. Ver aba Fontes e Referências.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Açúcar refinado</t>
+          <t>Bebida alcoólica</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Doces e Sobremesas</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7209,24 +7252,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Impacto direto nos triglicerídeos</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Piora diretamente os triglicerídeos; soma-se ao risco de sangramento da Aspirina + Ticagrelor.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>X</t>
@@ -7236,7 +7271,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Doces industrializados</t>
+          <t>Açúcar refinado</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7259,20 +7294,36 @@
           <t>evitar</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Impacto direto nos triglicerídeos</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chocolate amargo (70%+)</t>
+          <t>Doces industrializados</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7282,24 +7333,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2x/semana</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
-        </is>
-      </c>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
@@ -7312,47 +7359,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azeite de oliva extra virgem</t>
+          <t>Chocolate amargo (70%+)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gorduras e Temperos</t>
+          <t>Doces e Sobremesas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa</t>
+          <t>10 g</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1x/dia</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>2x/semana</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sugestão gerada por IA — confirmar com nutricionista/cardiologista</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Azeite de oliva extra virgem</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7362,37 +7409,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>evitar</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Preferir azeite</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>1x/dia</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7402,41 +7449,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Moderar</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>&lt; 5 g no total</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Somar sal de cozinha + industrializados</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Preferir azeite</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Creme de tahine</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7446,39 +7489,31 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Moderar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
+          <t>&lt; 5 g no total</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Somar sal de cozinha + industrializados</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>X</t>
@@ -7488,7 +7523,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sal light / substituto de sal (cloreto de potássio)</t>
+          <t>Creme de tahine</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7498,31 +7533,39 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Evitar</t>
+          <t>Liberado</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2 colheres de sopa (receita: 4 col. sopa de tahine, 1 col. sopa de limão, 1 col. sopa de azeite, sal e água)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Pasta de gergelim (tahine) + azeite: gorduras majoritariamente insaturadas, sem açúcar, boa fonte de cálcio/fibra — combina com o padrão de dieta mediterrânea recomendado. É calórico (rico em gordura), por isso porção moderada; controlar a quantidade de sal adicionado na receita. Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>X</t>
@@ -7532,7 +7575,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ervas e temperos naturais</t>
+          <t>Sal light / substituto de sal (cloreto de potássio)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7542,20 +7585,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Liberado</t>
+          <t>Evitar</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>à vontade</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>todos os dias</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>evitar</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Enalapril já tende a elevar o potássio; combinado com esse produto o risco de hipercalemia aumenta, ainda mais com a função renal pendente.</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
@@ -7572,12 +7619,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Vegetais e verduras em geral</t>
+          <t>Ervas e temperos naturais</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vegetais e Verduras</t>
+          <t>Gorduras e Temperos</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7595,26 +7642,14 @@
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>X</t>
@@ -7624,7 +7659,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Brócolis</t>
+          <t>Vegetais e verduras em geral</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7649,16 +7684,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Se entrar anticoagulante na medicação, revisar consumo de verde-escuros ricos em vitamina K</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>X</t>
@@ -7668,7 +7711,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Couve</t>
+          <t>Brócolis</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7693,7 +7736,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+          <t>Rico em fibras; combina bem com o padrão de dieta cardioprotetora recomendado.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -7712,7 +7755,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Espinafre</t>
+          <t>Couve</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7756,7 +7799,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Espinafre</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7779,22 +7822,18 @@
           <t>todos os dias</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Folha verde-escura rica em vitamina K — sem impacto hoje (nenhum anticoagulante em uso), mas vale reavaliar se isso mudar no tratamento.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>X</t>
@@ -7804,7 +7843,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cenoura</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7828,7 +7867,11 @@
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>X</t>
@@ -7848,7 +7891,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Abobrinha</t>
+          <t>Cenoura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7878,7 +7921,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>X</t>
@@ -7888,7 +7935,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Beterraba</t>
+          <t>Abobrinha</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7908,7 +7955,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -7928,7 +7975,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alface e folhas verdes (rúcula, agrião)</t>
+          <t>Beterraba</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7948,7 +7995,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -7958,11 +8005,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>X</t>
@@ -7972,7 +8015,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pepino</t>
+          <t>Alface e folhas verdes (rúcula, agrião)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8016,7 +8059,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Berinjela</t>
+          <t>Pepino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8036,7 +8079,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3x/semana</t>
+          <t>todos os dias</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -8046,7 +8089,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>X</t>
@@ -8056,7 +8103,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pimentão</t>
+          <t>Berinjela</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8076,7 +8123,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>todos os dias</t>
+          <t>3x/semana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -8086,11 +8133,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>X</t>
@@ -8100,7 +8143,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Repolho</t>
+          <t>Pimentão</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8130,8 +8173,52 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Repolho</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Vegetais e Verduras</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Liberado</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>à vontade</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>todos os dias</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>2 colheres de sopa (~30 g)</t>
+          <t>4 colheres de sopa (~30 g)</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="G17" s="13" t="inlineStr"/>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real (porção 40 g ≈ 1 unidade): 120 kcal, 170 mg de sódio, 1,6 g de gordura saturada, 1,2 g de fibras, 0 g de gordura trans, pouco açúcar adicionado (0,3 g). Sódio e gordura saturada acima do que se espera de uma tortilha simples — moderar a frequência e, se possível, somar com o restante do sódio do dia. Contém glúten (triticale). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: a porção declarada no rótulo é 40 g (1 tortilha de 33 g + um pedaço), com 120 kcal, 170 mg de sódio, 1,6 g de gordura saturada e 1,2 g de fibras. Para 1 tortilha inteira (33 g), isso equivale a ~99 kcal, 140 mg de sódio, 1,3 g de gordura saturada, 1,0 g de fibra, 0 g de gordura trans e 0,2 g de açúcar adicionado. Comparando dentro desta planilha: 1 pão francês integral tem cerca do dobro do sódio (279 mg) — o ponto de atenção da tortilha é mais a gordura saturada (4,0 g/100 g, acima do típico de uma tortilha simples) do que o sódio. Contém glúten (triticale). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       <c r="G19" s="13" t="inlineStr"/>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Rótulo real (a porção do rótulo é 40 g/½ xícara; valores abaixo recalculados para 20 g, para manter a mesma porção das demais granolas da planilha): ~91 kcal, 3,6 g de gordura (0,7 g saturada, 0 g trans), 12 g de carboidrato, 0,3 g de açúcar total e zero adicionado (adoçada com eritritol, maltitol e glicosídeos de esteviol — polióis, geralmente bem tolerados nessa quantidade), 2,2 g de proteína, 1,6 g de fibra, só 1,3 mg de sódio (praticamente sem sódio). Leva castanha-do-pará, castanha-de-caju, coco e óleo vegetal — por isso é calórica e tem gordura saturada relevante mesmo sendo zero açúcar: manter a porção, sem repetir a colher. Contém glúten (aveia, flocos de trigo); pode conter diversos alérgenos por contaminação cruzada (amendoim, leite, castanhas variadas, soja).</t>
+          <t>Rótulo real (a porção do rótulo é 40 g/½ xícara; valores abaixo recalculados para 20 g, para manter a mesma porção das demais granolas da planilha): ~91 kcal, 3,6 g de gordura (0,7 g saturada, 0 g trans), 12 g de carboidrato, 0,3 g de açúcar total e zero adicionado (adoçada com eritritol, maltitol e glicosídeos de esteviol — polióis, geralmente bem tolerados nessa quantidade), 2,2 g de proteína, 1,6 g de fibra, só 1,3 mg de sódio (praticamente sem sódio). Leva castanha-do-pará, castanha-de-caju, coco e óleo vegetal — por isso é calórica (455 kcal/100 g) mesmo sendo zero açúcar: manter a porção, sem repetir a colher. A gordura saturada, por outro lado, é baixa na porção (0,7 g) e menor que a da granola Castanha do Bem. Contém glúten (aveia, flocos de trigo); pode conter diversos alérgenos por contaminação cruzada (amendoim, leite, castanhas variadas, soja).</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2 colheres de sopa (~30 g)</t>
+          <t>4 colheres de sopa (~30 g)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rótulo real (porção 40 g ≈ 1 unidade): 120 kcal, 170 mg de sódio, 1,6 g de gordura saturada, 1,2 g de fibras, 0 g de gordura trans, pouco açúcar adicionado (0,3 g). Sódio e gordura saturada acima do que se espera de uma tortilha simples — moderar a frequência e, se possível, somar com o restante do sódio do dia. Contém glúten (triticale). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
+          <t>Rótulo real: a porção declarada no rótulo é 40 g (1 tortilha de 33 g + um pedaço), com 120 kcal, 170 mg de sódio, 1,6 g de gordura saturada e 1,2 g de fibras. Para 1 tortilha inteira (33 g), isso equivale a ~99 kcal, 140 mg de sódio, 1,3 g de gordura saturada, 1,0 g de fibra, 0 g de gordura trans e 0,2 g de açúcar adicionado. Comparando dentro desta planilha: 1 pão francês integral tem cerca do dobro do sódio (279 mg) — o ponto de atenção da tortilha é mais a gordura saturada (4,0 g/100 g, acima do típico de uma tortilha simples) do que o sódio. Contém glúten (triticale). Sugestão gerada por IA — confirmar com nutricionista/cardiologista.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rótulo real (a porção do rótulo é 40 g/½ xícara; valores abaixo recalculados para 20 g, para manter a mesma porção das demais granolas da planilha): ~91 kcal, 3,6 g de gordura (0,7 g saturada, 0 g trans), 12 g de carboidrato, 0,3 g de açúcar total e zero adicionado (adoçada com eritritol, maltitol e glicosídeos de esteviol — polióis, geralmente bem tolerados nessa quantidade), 2,2 g de proteína, 1,6 g de fibra, só 1,3 mg de sódio (praticamente sem sódio). Leva castanha-do-pará, castanha-de-caju, coco e óleo vegetal — por isso é calórica e tem gordura saturada relevante mesmo sendo zero açúcar: manter a porção, sem repetir a colher. Contém glúten (aveia, flocos de trigo); pode conter diversos alérgenos por contaminação cruzada (amendoim, leite, castanhas variadas, soja).</t>
+          <t>Rótulo real (a porção do rótulo é 40 g/½ xícara; valores abaixo recalculados para 20 g, para manter a mesma porção das demais granolas da planilha): ~91 kcal, 3,6 g de gordura (0,7 g saturada, 0 g trans), 12 g de carboidrato, 0,3 g de açúcar total e zero adicionado (adoçada com eritritol, maltitol e glicosídeos de esteviol — polióis, geralmente bem tolerados nessa quantidade), 2,2 g de proteína, 1,6 g de fibra, só 1,3 mg de sódio (praticamente sem sódio). Leva castanha-do-pará, castanha-de-caju, coco e óleo vegetal — por isso é calórica (455 kcal/100 g) mesmo sendo zero açúcar: manter a porção, sem repetir a colher. A gordura saturada, por outro lado, é baixa na porção (0,7 g) e menor que a da granola Castanha do Bem. Contém glúten (aveia, flocos de trigo); pode conter diversos alérgenos por contaminação cruzada (amendoim, leite, castanhas variadas, soja).</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/planilha/plano-alimentar-pos-infarto.xlsx
+++ b/planilha/plano-alimentar-pos-infarto.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Homem, 48 anos, IAM em 25/08/2026 (3 procedimentos, FE preservada 72% com hipocinesia segmentar leve). Dislipidemia mista: LDL 138 (meta pós-IAM &lt;50), HDL 34 (baixo), triglicerídeos 343 (muito alto), colesterol total 222 (alto). Placa carotídea leve (1–15%) já mostra aterosclerose além do evento agudo.</t>
+          <t>Homem, 48 anos, IAM em 25/08/2026 (3 procedimentos). Ecocardiograma de 29/09/2026: dentro da normalidade — FE 60% (Teichholz), sem alteração contrátil segmentar e função diastólica normal (o eco da internação, 26/08, mostrava FE 72% com hipocinesia segmentar leve; os dois valores de FE são normais, acima de 52%). Exames de 01/10/2026, já em uso contínuo dos remédios: LDL 47 (era 138 na internação), HDL 46 (era 34), triglicerídeos 70 (eram 343), colesterol total 108 (era 222) — perfil lipídico dentro das metas. Pontos ainda em aberto: HbA1c 5,9% (faixa de risco aumentado para diabetes) e função renal (creatinina 1,44, TFG 60, proteína na urina — ver 'Aviso pendente — função renal'). Placa carotídea leve (1–15%) já mostra aterosclerose além do evento agudo.</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Açúcar e carboidrato refinado — prioridade alta por causa dos triglicerídeos muito altos (343 mg/dL): refrigerante comum, doces, pão/arroz/massa branca em excesso.</t>
+          <t>Açúcar e carboidrato refinado — prioridade alta: a HbA1c de 01/10/2026 foi 5,9%, na faixa de 'risco aumentado para diabetes' (5,7 a 6,4%), mesmo patamar de antes do infarto (6,0% em 2022, 5,9% em 2025). Os triglicerídeos normalizaram (343 → 70), mas manter o cuidado: refrigerante comum, doces, pão/arroz/massa branca em excesso.</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Atenção especial — triglicerídeos</t>
+          <t>Atenção especial — triglicerídeos e glicemia</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>343 mg/dL é muito alto: o maior impacto individual costuma vir de cortar açúcar e álcool, não só gordura. Evitar refrigerante comum, suco industrializado, doces e bebida alcoólica quase por completo até reavaliação médica.</t>
+          <t>Triglicerídeos caíram de 343 mg/dL (internação) para 70 mg/dL (01/10/2026) — normal. Esse resultado vem da combinação remédio + dieta, então a orientação continua a mesma para não perdê-lo. Agora o motivo principal para segurar açúcar e carboidrato refinado é a glicemia: HbA1c 5,9% (risco aumentado para diabetes; glicose de jejum 92, normal). Continuar evitando refrigerante comum, suco industrializado e doces, e bebida alcoólica quase por completo (também por causa da dupla antiagregação). Perguntar ao médico se ele considera pré-diabetes e quando repetir a HbA1c.</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Meta pós-IAM é bem mais rígida que a da população geral, mas varia por diretriz: &lt;50 mg/dL (diretriz brasileira SBC 2017, usada pelo laboratório), &lt;40 mg/dL (categoria 'risco extremo' da diretriz SBC 2025, se preencher critérios adicionais) ou &lt;55 mg/dL (diretrizes ESC/EAS e ACC/AHA para risco muito alto) — pergunte ao médico qual meta ele está usando. A combinação estatina (Rosucor) + Ezetimiba já prescrita é sustentada pelo estudo IMPROVE-IT (LDL médio de 53,7 mg/dL com a combinação, vs. 69,5 mg/dL só com estatina, e menos eventos cardiovasculares). Fontes na aba 'Fontes e Referências'.</t>
+          <t>Resultado de 01/10/2026: LDL 47 mg/dL (era 138 na internação), já em uso de Rosucor + Ezetimiba. A meta pós-IAM varia por diretriz: &lt;50 mg/dL (SBC, risco muito alto — a tabela de metas do próprio laudo segue a diretriz SBC 2025) e &lt;55 mg/dL (ESC/EAS 2019, risco muito alto) — as duas já atingidas. Só estaria acima da meta se o médico usar &lt;40 mg/dL, da categoria 'risco extremo' da SBC 2025 (exige critérios adicionais) — pergunte ao médico qual meta ele está usando. A combinação estatina (Rosucor) + Ezetimiba já prescrita é sustentada pelo estudo IMPROVE-IT (LDL médio de 53,7 mg/dL com a combinação, vs. 69,5 mg/dL só com estatina, e menos eventos cardiovasculares). Fontes na aba 'Fontes e Referências'.</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Há suspeita ainda não confirmada de proteinúria (o exame certo a pedir é a relação albumina/creatinina urinária, ACR/RAC, padrão KDIGO) e duas elevações de creatinina/TFG durante a internação (TFG caiu para 57 na véspera da alta) — a última, aplicando o critério objetivo da KDIGO, já preenche Lesão Renal Aguda estágio 1 (não é diagnóstico médico, só a fórmula aplicada aos números). O padrão temporal é compatível com nefropatia por contraste dos 3 cateterismos (ESUR: pico em 3-5 dias, resolução em 7-14 dias). Enquanto não houver confirmação médica de que isso se resolveu, o plano NÃO aplica restrição renal (sódio/potássio/proteína) — apenas o cuidado cardiovascular abaixo. Revisar esta aba assim que o médico confirmar ou descartar o problema renal.</t>
+          <t>Exames de 01/10/2026 (cerca de 4 semanas após a alta): creatinina 1,44 mg/dL e TFG 60 — melhorou pouco em relação à alta (1,50 / 57), mas continua acima do seu valor de antes do infarto (1,05 em 2022, 1,12 em 2025). Ou seja, não se resolveu no prazo de 7-14 dias que a ESUR descreve para lesão renal por contraste. Parte dessa elevação pode ser efeito esperado do Enalapril (a diretriz ESC 2021 tolera alta de creatinina de até 50%), mas quem avalia é o médico. Ureia 61 mg/dL, acima da referência (17-48) — pode subir por causa do rim, de desidratação ou de consumo alto de proteína. A urina tipo I deu proteína + — primeiro sinal objetivo do que antes era só suspeita; o exame que confirma e quantifica é a relação albumina/creatinina urinária (ACR/RAC, padrão KDIGO), ainda não feito. A KDIGO só fala em doença renal crônica quando a alteração persiste por mais de 3 meses — por isso o reexame importa. Na internação, a queda de TFG para 57 preencheu o critério objetivo de Lesão Renal Aguda estágio 1 da KDIGO (fórmula aplicada aos números, não diagnóstico médico). Orientação: o plano continua SEM restrição renal formal (sódio/potássio/proteína), mas, por cautela, não exagerar em proteína — evitar suplementos tipo whey e dietas hiperproteicas — até o médico avaliar. Revisar esta aba assim que o médico se posicionar.</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Enalapril pode elevar o potássio do sangue (reduz a aldosterona). Evitar sal light/substitutos de sal (ricos em cloreto de potássio) e suplementos de potássio sem orientação médica — risco bem documentado de hipercalemia. O potássio (4,9) e a creatinina (1,50) da alta ficam dentro da faixa considerada tolerável por uma diretriz de insuficiência cardíaca (ESC 2021) para manter o Enalapril — informação tranquilizadora, mas essa mesma diretriz recomenda reexame de potássio/creatinina em 1-2 semanas, e reforça evitar sal light por precaução até lá. Fontes: aba 'Fontes e Referências', linha 3 (Enalapril) e 15 (limiares ESC).</t>
+          <t>Enalapril pode elevar o potássio do sangue (reduz a aldosterona). Evitar sal light/substitutos de sal (ricos em cloreto de potássio) e suplementos de potássio sem orientação médica — risco bem documentado de hipercalemia. Na alta, potássio 4,9 e creatinina 1,50; no reexame de 01/10/2026, potássio 4,7 e creatinina 1,44 — os dois dentro da faixa considerada tolerável por uma diretriz de insuficiência cardíaca (ESC 2021) para manter o Enalapril. Continuar evitando sal light. Fontes: aba 'Fontes e Referências', linha 3 (Enalapril) e 15 (limiares ESC).</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Metas de LDL pós-infarto: &lt;50 mg/dL (SBC 2017); &lt;40 mg/dL na categoria "risco extremo" (SBC 2025, com critérios adicionais); &lt;55 mg/dL (ESC/EAS 2019 e ACC/AHA, risco muito alto)</t>
+          <t>Metas de LDL pós-infarto: &lt;50 mg/dL (SBC, risco muito alto — já em 2017 e mantida em 2025, tabela usada no laudo do laboratório); &lt;40 mg/dL na categoria "risco extremo" (SBC 2025, com critérios adicionais); &lt;55 mg/dL (ESC/EAS 2019, risco muito alto)</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>HbA1c ≥6,5% sugere diabetes prévio; abaixo de 5,7% (caso do paciente) é consistente com hiperglicemia de estresse, não diabetes</t>
+          <t>HbA1c ≥6,5% sugere diabetes; 5,7 a 6,4% é faixa de risco aumentado (pré-diabetes). Paciente: 5,5% na internação, mas 5,9% em 01/10/2026 (e 6,0% em 2022, 5,9% em 2025) — o valor da internação parece fora da curva; perguntar ao médico</t>
         </is>
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>American Diabetes Association — Standards of Care in Diabetes, edições 2024-2026</t>
+          <t>American Diabetes Association — Standards of Care in Diabetes 2026: seção 2, Diagnóstico (Diabetes Care 2026;49 Supl. 1:S27–S49, citada no próprio laudo) e seção 16, Hospital (link)</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
